--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,38 +530,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 15:40</t>
+          <t>2025-07-28 16:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.10353</v>
+        <v>0.58949</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.10052</v>
+        <v>0.59288</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.11283</v>
+        <v>0.58363</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.09</v>
+        <v>1.73</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:28</t>
+          <t>2025-07-28 16:33</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.26608</v>
+        <v>1.36015</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.26114</v>
+        <v>1.36347</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.27162</v>
+        <v>1.35395</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.12</v>
+        <v>1.87</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:05</t>
+          <t>2025-07-28 16:10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>149.27654</v>
+        <v>1.27368</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>149.56825</v>
+        <v>1.26993</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>148.53092</v>
+        <v>1.28025</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:15</t>
+          <t>2025-07-28 15:47</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.65742</v>
+        <v>0.87907</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.65307</v>
+        <v>0.87601</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6642400000000001</v>
+        <v>0.88886</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.57</v>
+        <v>3.19</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:04:04</t>
+          <t>2025-07-28 16:14:05</t>
         </is>
       </c>
     </row>
@@ -861,36 +861,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 15:40</t>
+          <t>2025-07-28 16:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.10353</v>
+        <v>0.58949</v>
       </c>
       <c r="E2" t="n">
-        <v>1.10052</v>
+        <v>0.59288</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11283</v>
+        <v>0.58363</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.09</v>
+        <v>1.73</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 15:55</t>
+          <t>2025-07-28 16:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,22 +915,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.88518</v>
+        <v>1.27296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.88153</v>
+        <v>1.26912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.89268</v>
+        <v>1.28189</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H3" t="n">
         <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -941,12 +941,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 16:28</t>
+          <t>2025-07-28 16:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -955,33 +955,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.26608</v>
+        <v>1.10392</v>
       </c>
       <c r="E4" t="n">
-        <v>1.26114</v>
+        <v>1.09981</v>
       </c>
       <c r="F4" t="n">
-        <v>1.27162</v>
+        <v>1.11355</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.12</v>
+        <v>2.34</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 16:02</t>
+          <t>2025-07-28 15:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -995,38 +995,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.10501</v>
+        <v>1.10635</v>
       </c>
       <c r="E5" t="n">
-        <v>1.10244</v>
+        <v>1.10404</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11384</v>
+        <v>1.11404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 16:27</t>
+          <t>2025-07-28 16:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1035,62 +1035,62 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.26437</v>
+        <v>1.36015</v>
       </c>
       <c r="E6" t="n">
-        <v>1.26868</v>
+        <v>1.36347</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25511</v>
+        <v>1.35395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 16:18</t>
+          <t>2025-07-28 15:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.35864</v>
+        <v>149.26014</v>
       </c>
       <c r="E7" t="n">
-        <v>1.36199</v>
+        <v>148.98974</v>
       </c>
       <c r="F7" t="n">
-        <v>1.34966</v>
+        <v>150.01281</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1101,36 +1101,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 15:53</t>
+          <t>2025-07-28 16:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.10032</v>
+        <v>0.65602</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09825</v>
+        <v>0.65811</v>
       </c>
       <c r="F8" t="n">
-        <v>1.10994</v>
+        <v>0.6519</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>4.64</v>
+        <v>1.98</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1141,36 +1141,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:26</t>
+          <t>2025-07-28 16:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.3697</v>
+        <v>1.27178</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36514</v>
+        <v>1.27625</v>
       </c>
       <c r="F9" t="n">
-        <v>1.37922</v>
+        <v>1.265</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 15:48</t>
+          <t>2025-07-28 15:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1195,33 +1195,33 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.65898</v>
+        <v>0.66004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65434</v>
+        <v>0.65789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66611</v>
+        <v>0.665</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 16:05</t>
+          <t>2025-07-28 16:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1231,26 +1231,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.10987</v>
+        <v>1.10039</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1127</v>
+        <v>1.09594</v>
       </c>
       <c r="F11" t="n">
-        <v>1.10465</v>
+        <v>1.10777</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1261,52 +1261,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 16:31</t>
+          <t>2025-07-28 16:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.10171</v>
+        <v>1.26382</v>
       </c>
       <c r="E12" t="n">
-        <v>1.09805</v>
+        <v>1.26865</v>
       </c>
       <c r="F12" t="n">
-        <v>1.10753</v>
+        <v>1.25472</v>
       </c>
       <c r="G12" t="n">
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="I12" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 16:05</t>
+          <t>2025-07-28 16:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1315,78 +1315,78 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>149.27654</v>
+        <v>1.10051</v>
       </c>
       <c r="E13" t="n">
-        <v>149.56825</v>
+        <v>1.10462</v>
       </c>
       <c r="F13" t="n">
-        <v>148.53092</v>
+        <v>1.0959</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>1.12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 16:15</t>
+          <t>2025-07-28 16:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.65742</v>
+        <v>0.88506</v>
       </c>
       <c r="E14" t="n">
-        <v>0.65307</v>
+        <v>0.88976</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6642400000000001</v>
+        <v>0.87636</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 16:02</t>
+          <t>2025-07-28 16:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1395,38 +1395,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.8805500000000001</v>
+        <v>1.27368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8781600000000001</v>
+        <v>1.26993</v>
       </c>
       <c r="F15" t="n">
-        <v>0.88547</v>
+        <v>1.28025</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 16:26</t>
+          <t>2025-07-28 15:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1435,26 +1435,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.65801</v>
+        <v>0.87907</v>
       </c>
       <c r="E16" t="n">
-        <v>0.65529</v>
+        <v>0.87601</v>
       </c>
       <c r="F16" t="n">
-        <v>0.66753</v>
+        <v>0.88886</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H16" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.49</v>
+        <v>3.19</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,14 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -460,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:44</t>
+          <t>2025-07-28 16:29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -544,24 +537,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.58949</v>
+        <v>0.59027</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.59288</v>
+        <v>0.59471</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.58363</v>
+        <v>0.5813</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,12 +565,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:33</t>
+          <t>2025-07-28 16:03</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -586,24 +579,24 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.36015</v>
+        <v>0.59092</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.36347</v>
+        <v>0.59559</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.35395</v>
+        <v>0.58222</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +607,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:10</t>
+          <t>2025-07-28 15:53</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.27368</v>
+        <v>148.7591</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.26993</v>
+        <v>148.97191</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.28025</v>
+        <v>148.00594</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.75</v>
+        <v>3.54</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,40 +649,82 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 15:47</t>
+          <t>2025-07-28 16:34</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.59032</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.58405</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 16:07</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>USDCHF</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.87907</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.87601</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.88886</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.88256</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.88551</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.87266</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>82.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -710,14 +745,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -727,68 +762,68 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:14:05</t>
+          <t>2025-07-28 16:19:05</t>
         </is>
       </c>
     </row>
@@ -807,52 +842,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -861,12 +896,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:44</t>
+          <t>2025-07-28 16:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -875,73 +910,73 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.58949</v>
+        <v>0.65446</v>
       </c>
       <c r="E2" t="n">
-        <v>0.59288</v>
+        <v>0.65779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.58363</v>
+        <v>0.64612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I2" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 16:03</t>
+          <t>2025-07-28 16:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.27296</v>
+        <v>0.59027</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26912</v>
+        <v>0.59471</v>
       </c>
       <c r="F3" t="n">
-        <v>1.28189</v>
+        <v>0.5813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="n">
         <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 16:08</t>
+          <t>2025-07-28 16:31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -955,78 +990,78 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10392</v>
+        <v>1.10518</v>
       </c>
       <c r="E4" t="n">
-        <v>1.09981</v>
+        <v>1.10121</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11355</v>
+        <v>1.11047</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 15:58</t>
+          <t>2025-07-28 16:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.10635</v>
+        <v>0.59092</v>
       </c>
       <c r="E5" t="n">
-        <v>1.10404</v>
+        <v>0.59559</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11404</v>
+        <v>0.58222</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="I5" t="n">
-        <v>3.33</v>
+        <v>1.86</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 16:33</t>
+          <t>2025-07-28 15:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1035,22 +1070,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.36015</v>
+        <v>148.7591</v>
       </c>
       <c r="E6" t="n">
-        <v>1.36347</v>
+        <v>148.97191</v>
       </c>
       <c r="F6" t="n">
-        <v>1.35395</v>
+        <v>148.00594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>1.87</v>
+        <v>3.54</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1061,12 +1096,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 15:51</t>
+          <t>2025-07-28 16:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1075,38 +1110,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>149.26014</v>
+        <v>0.58971</v>
       </c>
       <c r="E7" t="n">
-        <v>148.98974</v>
+        <v>0.58547</v>
       </c>
       <c r="F7" t="n">
-        <v>150.01281</v>
+        <v>0.5941</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 16:01</t>
+          <t>2025-07-28 16:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1115,38 +1150,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.65602</v>
+        <v>0.59032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.65811</v>
+        <v>0.5938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6519</v>
+        <v>0.58405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:38</t>
+          <t>2025-07-28 16:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1155,22 +1190,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.27178</v>
+        <v>0.65982</v>
       </c>
       <c r="E9" t="n">
-        <v>1.27625</v>
+        <v>0.6634100000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.265</v>
+        <v>0.65043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>1.51</v>
+        <v>2.62</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1181,12 +1216,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 15:46</t>
+          <t>2025-07-28 16:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1195,38 +1230,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.66004</v>
+        <v>1.10384</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65789</v>
+        <v>1.09903</v>
       </c>
       <c r="F10" t="n">
-        <v>0.665</v>
+        <v>1.10812</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.89</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 16:03</t>
+          <t>2025-07-28 15:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1235,22 +1270,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.10039</v>
+        <v>0.59185</v>
       </c>
       <c r="E11" t="n">
-        <v>1.09594</v>
+        <v>0.58911</v>
       </c>
       <c r="F11" t="n">
-        <v>1.10777</v>
+        <v>0.60011</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>1.66</v>
+        <v>3.02</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1261,52 +1296,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 16:21</t>
+          <t>2025-07-28 16:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.26382</v>
+        <v>150.20715</v>
       </c>
       <c r="E12" t="n">
-        <v>1.26865</v>
+        <v>149.90187</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25472</v>
+        <v>150.6095</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 16:35</t>
+          <t>2025-07-28 16:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1315,22 +1350,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10051</v>
+        <v>0.58912</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10462</v>
+        <v>0.59309</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0959</v>
+        <v>0.5834</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89</v>
+        <v>0.66</v>
       </c>
       <c r="I13" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1341,7 +1376,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 16:24</t>
+          <t>2025-07-28 16:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1355,38 +1390,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.88506</v>
+        <v>0.88256</v>
       </c>
       <c r="E14" t="n">
-        <v>0.88976</v>
+        <v>0.88551</v>
       </c>
       <c r="F14" t="n">
-        <v>0.87636</v>
+        <v>0.87266</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>1.85</v>
+        <v>3.36</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 16:10</t>
+          <t>2025-07-28 16:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1395,66 +1430,66 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.27368</v>
+        <v>1.36602</v>
       </c>
       <c r="E15" t="n">
-        <v>1.26993</v>
+        <v>1.36135</v>
       </c>
       <c r="F15" t="n">
-        <v>1.28025</v>
+        <v>1.37252</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 15:47</t>
+          <t>2025-07-28 16:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.87907</v>
+        <v>0.58751</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87601</v>
+        <v>0.5906400000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88886</v>
+        <v>0.57763</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,13 +84,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -523,38 +530,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:29</t>
+          <t>2025-07-28 16:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.59027</v>
+        <v>0.87966</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.59471</v>
+        <v>0.87537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5813</v>
+        <v>0.88524</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -565,30 +572,30 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:03</t>
+          <t>2025-07-28 17:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.59092</v>
+        <v>0.87758</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.59559</v>
+        <v>0.88067</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.58222</v>
+        <v>0.87008</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -596,7 +603,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -607,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 15:53</t>
+          <t>2025-07-28 16:58</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>148.7591</v>
+        <v>0.65779</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.97191</v>
+        <v>0.65987</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>148.00594</v>
+        <v>0.6505300000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -649,82 +656,40 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:34</t>
+          <t>2025-07-28 16:55</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.59032</v>
+        <v>0.87915</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5938</v>
+        <v>0.88223</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.58405</v>
+        <v>0.87376</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 16:07</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>USDCHF</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.88256</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.88551</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.87266</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>82.0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -745,14 +710,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -762,68 +727,68 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>SELL Signals</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SELL Signals</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.89</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:19:05</t>
+          <t>2025-07-28 16:34:07</t>
         </is>
       </c>
     </row>
@@ -842,52 +807,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -896,36 +861,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:38</t>
+          <t>2025-07-28 16:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.65446</v>
+        <v>1.10302</v>
       </c>
       <c r="E2" t="n">
-        <v>0.65779</v>
+        <v>1.09921</v>
       </c>
       <c r="F2" t="n">
-        <v>0.64612</v>
+        <v>1.11156</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -936,36 +901,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 16:29</t>
+          <t>2025-07-28 16:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.59027</v>
+        <v>0.87966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.59471</v>
+        <v>0.87537</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5813</v>
+        <v>0.88524</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -976,7 +941,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 16:31</t>
+          <t>2025-07-28 16:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -990,78 +955,78 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10518</v>
+        <v>1.10177</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10121</v>
+        <v>1.09809</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11047</v>
+        <v>1.10796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 16:03</t>
+          <t>2025-07-28 16:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.59092</v>
+        <v>0.8822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.59559</v>
+        <v>0.87761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58222</v>
+        <v>0.89046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I5" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 15:53</t>
+          <t>2025-07-28 17:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,22 +1035,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>148.7591</v>
+        <v>0.87758</v>
       </c>
       <c r="E6" t="n">
-        <v>148.97191</v>
+        <v>0.88067</v>
       </c>
       <c r="F6" t="n">
-        <v>148.00594</v>
+        <v>0.87008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H6" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>3.54</v>
+        <v>2.42</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1096,7 +1061,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 16:36</t>
+          <t>2025-07-28 16:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,38 +1075,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58971</v>
+        <v>0.59078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.58547</v>
+        <v>0.58586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5941</v>
+        <v>0.60039</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I7" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 16:34</t>
+          <t>2025-07-28 16:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1150,22 +1115,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.59032</v>
+        <v>0.65779</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5938</v>
+        <v>0.65987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.58405</v>
+        <v>0.6505300000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1176,40 +1141,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:19</t>
+          <t>2025-07-28 16:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.65982</v>
+        <v>149.15831</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6634100000000001</v>
+        <v>148.73838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.65043</v>
+        <v>150.1414</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1186,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1230,22 +1195,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.10384</v>
+        <v>0.87881</v>
       </c>
       <c r="E10" t="n">
-        <v>1.09903</v>
+        <v>0.87459</v>
       </c>
       <c r="F10" t="n">
-        <v>1.10812</v>
+        <v>0.88583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H10" t="n">
         <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1256,7 +1221,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 15:54</t>
+          <t>2025-07-28 16:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1270,62 +1235,62 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.59185</v>
+        <v>0.59115</v>
       </c>
       <c r="E11" t="n">
-        <v>0.58911</v>
+        <v>0.5878</v>
       </c>
       <c r="F11" t="n">
-        <v>0.60011</v>
+        <v>0.59581</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="I11" t="n">
-        <v>3.02</v>
+        <v>1.39</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 16:11</t>
+          <t>2025-07-28 16:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>150.20715</v>
+        <v>1.26444</v>
       </c>
       <c r="E12" t="n">
-        <v>149.90187</v>
+        <v>1.2683</v>
       </c>
       <c r="F12" t="n">
-        <v>150.6095</v>
+        <v>1.25799</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1336,12 +1301,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 16:06</t>
+          <t>2025-07-28 16:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1350,22 +1315,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.58912</v>
+        <v>0.6543600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.59309</v>
+        <v>0.65788</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5834</v>
+        <v>0.64725</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H13" t="n">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1376,76 +1341,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 16:07</t>
+          <t>2025-07-28 16:46</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.88256</v>
+        <v>1.36578</v>
       </c>
       <c r="E14" t="n">
-        <v>0.88551</v>
+        <v>1.36114</v>
       </c>
       <c r="F14" t="n">
-        <v>0.87266</v>
+        <v>1.37219</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="I14" t="n">
-        <v>3.36</v>
+        <v>1.38</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 16:29</t>
+          <t>2025-07-28 16:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.36602</v>
+        <v>1.09923</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36135</v>
+        <v>1.10336</v>
       </c>
       <c r="F15" t="n">
-        <v>1.37252</v>
+        <v>1.09421</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1456,12 +1421,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 16:44</t>
+          <t>2025-07-28 16:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1470,26 +1435,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.58751</v>
+        <v>0.87915</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5906400000000001</v>
+        <v>0.88223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.57763</v>
+        <v>0.87376</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>3.16</v>
+        <v>1.75</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:56</t>
+          <t>2025-07-28 19:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.87966</v>
+        <v>0.6569199999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.87537</v>
+        <v>0.65464</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.88524</v>
+        <v>0.66323</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.3</v>
+        <v>2.77</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 17:00</t>
+          <t>2025-07-28 19:29</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.87758</v>
+        <v>1.36116</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.88067</v>
+        <v>1.35649</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.87008</v>
+        <v>1.36818</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,12 +614,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:58</t>
+          <t>2025-07-28 19:24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.65779</v>
+        <v>1.27154</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.65987</v>
+        <v>1.27653</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6505300000000001</v>
+        <v>1.26573</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3.5</v>
+        <v>1.16</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:55</t>
+          <t>2025-07-28 19:40</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.87915</v>
+        <v>0.65813</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.88223</v>
+        <v>0.65364</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.87376</v>
+        <v>0.6622400000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.75</v>
+        <v>0.92</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:34:07</t>
+          <t>2025-07-28 19:25:28</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 16:07</t>
+          <t>2025-07-28 19:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -875,38 +875,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.10302</v>
+        <v>0.6569199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1.09921</v>
+        <v>0.65464</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11156</v>
+        <v>0.66323</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.77</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 16:56</t>
+          <t>2025-07-28 19:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -915,22 +915,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.87966</v>
+        <v>1.36116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.87537</v>
+        <v>1.35649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88524</v>
+        <v>1.36818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H3" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -941,12 +941,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 16:47</t>
+          <t>2025-07-28 19:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -955,118 +955,118 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10177</v>
+        <v>1.36194</v>
       </c>
       <c r="E4" t="n">
-        <v>1.09809</v>
+        <v>1.35947</v>
       </c>
       <c r="F4" t="n">
-        <v>1.10796</v>
+        <v>1.3684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>2.61</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 16:26</t>
+          <t>2025-07-28 19:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8822</v>
+        <v>1.27154</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87761</v>
+        <v>1.27653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.89046</v>
+        <v>1.26573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 17:00</t>
+          <t>2025-07-28 19:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.87758</v>
+        <v>150.00672</v>
       </c>
       <c r="E6" t="n">
-        <v>0.88067</v>
+        <v>149.69719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.87008</v>
+        <v>150.70286</v>
       </c>
       <c r="G6" t="n">
         <v>0.09</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 16:12</t>
+          <t>2025-07-28 19:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1075,22 +1075,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.59078</v>
+        <v>1.27111</v>
       </c>
       <c r="E7" t="n">
-        <v>0.58586</v>
+        <v>1.26667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.60039</v>
+        <v>1.28048</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1101,92 +1101,92 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 16:58</t>
+          <t>2025-07-28 19:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.65779</v>
+        <v>0.58896</v>
       </c>
       <c r="E8" t="n">
-        <v>0.65987</v>
+        <v>0.5866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6505300000000001</v>
+        <v>0.59733</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 16:26</t>
+          <t>2025-07-28 19:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149.15831</v>
+        <v>1.10897</v>
       </c>
       <c r="E9" t="n">
-        <v>148.73838</v>
+        <v>1.11237</v>
       </c>
       <c r="F9" t="n">
-        <v>150.1414</v>
+        <v>1.10414</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="I9" t="n">
-        <v>2.34</v>
+        <v>1.42</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 16:34</t>
+          <t>2025-07-28 19:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1195,78 +1195,78 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.87881</v>
+        <v>0.65579</v>
       </c>
       <c r="E10" t="n">
-        <v>0.87459</v>
+        <v>0.65228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.88583</v>
+        <v>0.6625799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 16:31</t>
+          <t>2025-07-28 19:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.59115</v>
+        <v>0.65563</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5878</v>
+        <v>0.6601</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59581</v>
+        <v>0.65027</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 16:50</t>
+          <t>2025-07-28 19:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1275,33 +1275,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.26444</v>
+        <v>0.59095</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2683</v>
+        <v>0.59576</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25799</v>
+        <v>0.58178</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="I12" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 16:07</t>
+          <t>2025-07-28 19:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1311,42 +1311,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.6543600000000001</v>
+        <v>0.65813</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65788</v>
+        <v>0.65364</v>
       </c>
       <c r="F13" t="n">
-        <v>0.64725</v>
+        <v>0.6622400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="I13" t="n">
-        <v>2.02</v>
+        <v>0.92</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 16:46</t>
+          <t>2025-07-28 19:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1355,22 +1355,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.36578</v>
+        <v>1.27136</v>
       </c>
       <c r="E14" t="n">
-        <v>1.36114</v>
+        <v>1.26819</v>
       </c>
       <c r="F14" t="n">
-        <v>1.37219</v>
+        <v>1.27863</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H14" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1381,52 +1381,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 16:04</t>
+          <t>2025-07-28 19:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.09923</v>
+        <v>0.87943</v>
       </c>
       <c r="E15" t="n">
-        <v>1.10336</v>
+        <v>0.87619</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09421</v>
+        <v>0.88415</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 16:55</t>
+          <t>2025-07-28 19:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1435,26 +1435,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.87915</v>
+        <v>1.26355</v>
       </c>
       <c r="E16" t="n">
-        <v>0.88223</v>
+        <v>1.26715</v>
       </c>
       <c r="F16" t="n">
-        <v>0.87376</v>
+        <v>1.25387</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.75</v>
+        <v>2.69</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:44</t>
+          <t>2025-07-28 19:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -540,28 +540,28 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6569199999999999</v>
+        <v>0.6591399999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.65464</v>
+        <v>0.66237</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.66323</v>
+        <v>0.6515</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.77</v>
+        <v>2.37</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:29</t>
+          <t>2025-07-28 19:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,28 +582,28 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.36116</v>
+        <v>1.36221</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.35649</v>
+        <v>1.36531</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.36818</v>
+        <v>1.3559</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.51</v>
+        <v>2.03</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:24</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.27154</v>
+        <v>0.58913</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.27653</v>
+        <v>0.59282</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.26573</v>
+        <v>0.57921</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.16</v>
+        <v>2.69</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,40 +656,82 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:40</t>
+          <t>2025-07-28 19:11</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.65813</v>
+        <v>1.26699</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.65364</v>
+        <v>1.26497</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6622400000000001</v>
+        <v>1.27588</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.92</v>
+        <v>4.42</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 19:08</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>149.11418</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>149.31518</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>148.20714</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>66.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -733,7 +775,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -743,7 +785,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +795,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -764,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -776,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -788,7 +830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:25:28</t>
+          <t>2025-07-28 19:35:29</t>
         </is>
       </c>
     </row>
@@ -861,7 +903,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:44</t>
+          <t>2025-07-28 19:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -871,26 +913,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6569199999999999</v>
+        <v>0.6591399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.65464</v>
+        <v>0.66237</v>
       </c>
       <c r="F2" t="n">
-        <v>0.66323</v>
+        <v>0.6515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="I2" t="n">
-        <v>2.77</v>
+        <v>2.37</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -901,47 +943,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 19:29</t>
+          <t>2025-07-28 19:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.36116</v>
+        <v>1.2672</v>
       </c>
       <c r="E3" t="n">
-        <v>1.35649</v>
+        <v>1.27119</v>
       </c>
       <c r="F3" t="n">
-        <v>1.36818</v>
+        <v>1.25817</v>
       </c>
       <c r="G3" t="n">
         <v>0.09</v>
       </c>
       <c r="H3" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.51</v>
+        <v>2.27</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 19:38</t>
+          <t>2025-07-28 19:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -951,42 +993,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.36194</v>
+        <v>1.36221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.35947</v>
+        <v>1.36531</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3684</v>
+        <v>1.3559</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>2.61</v>
+        <v>2.03</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 19:24</t>
+          <t>2025-07-28 19:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -995,62 +1037,62 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.27154</v>
+        <v>0.65622</v>
       </c>
       <c r="E5" t="n">
-        <v>1.27653</v>
+        <v>0.6601</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26573</v>
+        <v>0.64627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1.16</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 19:34</t>
+          <t>2025-07-28 19:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150.00672</v>
+        <v>0.58906</v>
       </c>
       <c r="E6" t="n">
-        <v>149.69719</v>
+        <v>0.59294</v>
       </c>
       <c r="F6" t="n">
-        <v>150.70286</v>
+        <v>0.5839</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1061,12 +1103,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 19:02</t>
+          <t>2025-07-28 20:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1075,38 +1117,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.27111</v>
+        <v>0.88078</v>
       </c>
       <c r="E7" t="n">
-        <v>1.26667</v>
+        <v>0.87585</v>
       </c>
       <c r="F7" t="n">
-        <v>1.28048</v>
+        <v>0.88957</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 19:11</t>
+          <t>2025-07-28 19:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1115,22 +1157,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.58896</v>
+        <v>1.3664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5866</v>
+        <v>1.36228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.59733</v>
+        <v>1.37606</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="I8" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1141,12 +1183,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:03</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1155,38 +1197,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.10897</v>
+        <v>0.58913</v>
       </c>
       <c r="E9" t="n">
-        <v>1.11237</v>
+        <v>0.59282</v>
       </c>
       <c r="F9" t="n">
-        <v>1.10414</v>
+        <v>0.57921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>1.42</v>
+        <v>2.69</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:02</t>
+          <t>2025-07-28 19:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1195,38 +1237,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.65579</v>
+        <v>0.58736</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65228</v>
+        <v>0.58366</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6625799999999999</v>
+        <v>0.59299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:21</t>
+          <t>2025-07-28 19:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1235,38 +1277,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.65563</v>
+        <v>1.09978</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6601</v>
+        <v>1.10314</v>
       </c>
       <c r="F11" t="n">
-        <v>0.65027</v>
+        <v>1.09483</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 19:41</t>
+          <t>2025-07-28 20:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1275,22 +1317,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.59095</v>
+        <v>0.65556</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59576</v>
+        <v>0.65854</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58178</v>
+        <v>0.6476499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="I12" t="n">
-        <v>1.91</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1301,12 +1343,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 19:40</t>
+          <t>2025-07-28 19:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1315,33 +1357,33 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.65813</v>
+        <v>1.36078</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65364</v>
+        <v>1.3558</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6622400000000001</v>
+        <v>1.36569</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 19:24</t>
+          <t>2025-07-28 19:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1355,102 +1397,102 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.27136</v>
+        <v>1.26699</v>
       </c>
       <c r="E14" t="n">
-        <v>1.26819</v>
+        <v>1.26497</v>
       </c>
       <c r="F14" t="n">
-        <v>1.27863</v>
+        <v>1.27588</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H14" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>4.42</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 19:24</t>
+          <t>2025-07-28 19:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.87943</v>
+        <v>149.11418</v>
       </c>
       <c r="E15" t="n">
-        <v>0.87619</v>
+        <v>149.31518</v>
       </c>
       <c r="F15" t="n">
-        <v>0.88415</v>
+        <v>148.20714</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>1.45</v>
+        <v>4.51</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 19:21</t>
+          <t>2025-07-28 19:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.26355</v>
+        <v>0.88032</v>
       </c>
       <c r="E16" t="n">
-        <v>1.26715</v>
+        <v>0.87825</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25387</v>
+        <v>0.8867</v>
       </c>
       <c r="G16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:46</t>
+          <t>2025-07-28 20:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6591399999999999</v>
+        <v>0.88091</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.66237</v>
+        <v>0.88518</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6515</v>
+        <v>0.87119</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:34</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>USDCAD</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.36221</v>
+        <v>0.59179</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.36531</v>
+        <v>0.58828</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.3559</v>
+        <v>0.5992</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:54</t>
+          <t>2025-07-28 19:53</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.58913</v>
+        <v>150.15321</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.59282</v>
+        <v>149.91022</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.57921</v>
+        <v>150.6297</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.69</v>
+        <v>1.96</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:11</t>
+          <t>2025-07-28 19:28</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.26699</v>
+        <v>148.8192</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.26497</v>
+        <v>149.03316</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.27588</v>
+        <v>148.41725</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4.42</v>
+        <v>1.88</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -698,12 +698,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:08</t>
+          <t>2025-07-28 20:02</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -712,26 +712,110 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>149.11418</v>
+        <v>1.37045</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>149.31518</v>
+        <v>1.37409</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>148.20714</v>
+        <v>1.36562</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.51</v>
+        <v>1.33</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 19:17</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1.27183</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.2696</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1.28111</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 19:36</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.87649</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.88683</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77.0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -775,7 +859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -806,7 +890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -818,7 +902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.54</t>
         </is>
       </c>
     </row>
@@ -830,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:35:29</t>
+          <t>2025-07-28 19:45:30</t>
         </is>
       </c>
     </row>
@@ -903,12 +987,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:46</t>
+          <t>2025-07-28 20:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -917,22 +1001,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6591399999999999</v>
+        <v>0.88091</v>
       </c>
       <c r="E2" t="n">
-        <v>0.66237</v>
+        <v>0.88518</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6515</v>
+        <v>0.87119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="I2" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -943,47 +1027,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 19:55</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2672</v>
+        <v>0.59179</v>
       </c>
       <c r="E3" t="n">
-        <v>1.27119</v>
+        <v>0.58828</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25817</v>
+        <v>0.5992</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 19:34</t>
+          <t>2025-07-28 19:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -993,42 +1077,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.36221</v>
+        <v>1.36364</v>
       </c>
       <c r="E4" t="n">
-        <v>1.36531</v>
+        <v>1.3615</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3559</v>
+        <v>1.37179</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2.03</v>
+        <v>3.81</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 19:45</t>
+          <t>2025-07-28 19:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1037,22 +1121,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.65622</v>
+        <v>1.36515</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6601</v>
+        <v>1.36797</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64627</v>
+        <v>1.36039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1063,132 +1147,132 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 19:15</t>
+          <t>2025-07-28 19:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.58906</v>
+        <v>150.15321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.59294</v>
+        <v>149.91022</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5839</v>
+        <v>150.6297</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:02</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.88078</v>
+        <v>1.10416</v>
       </c>
       <c r="E7" t="n">
-        <v>0.87585</v>
+        <v>1.10896</v>
       </c>
       <c r="F7" t="n">
-        <v>0.88957</v>
+        <v>1.09589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 19:59</t>
+          <t>2025-07-28 19:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3664</v>
+        <v>1.27152</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36228</v>
+        <v>1.27443</v>
       </c>
       <c r="F8" t="n">
-        <v>1.37606</v>
+        <v>1.26464</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:54</t>
+          <t>2025-07-28 19:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1197,38 +1281,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.58913</v>
+        <v>1.36167</v>
       </c>
       <c r="E9" t="n">
-        <v>0.59282</v>
+        <v>1.36465</v>
       </c>
       <c r="F9" t="n">
-        <v>0.57921</v>
+        <v>1.35637</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:27</t>
+          <t>2025-07-28 19:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1237,38 +1321,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.58736</v>
+        <v>1.27579</v>
       </c>
       <c r="E10" t="n">
-        <v>0.58366</v>
+        <v>1.27373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.59299</v>
+        <v>1.28514</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.52</v>
+        <v>4.55</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:37</t>
+          <t>2025-07-28 19:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1277,38 +1361,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.09978</v>
+        <v>0.88015</v>
       </c>
       <c r="E11" t="n">
-        <v>1.10314</v>
+        <v>0.88296</v>
       </c>
       <c r="F11" t="n">
-        <v>1.09483</v>
+        <v>0.87033</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="I11" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:00</t>
+          <t>2025-07-28 19:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1317,33 +1401,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.65556</v>
+        <v>148.8192</v>
       </c>
       <c r="E12" t="n">
-        <v>0.65854</v>
+        <v>149.03316</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6476499999999999</v>
+        <v>148.41725</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 19:12</t>
+          <t>2025-07-28 20:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1353,106 +1437,106 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.36078</v>
+        <v>1.37045</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3558</v>
+        <v>1.37409</v>
       </c>
       <c r="F13" t="n">
-        <v>1.36569</v>
+        <v>1.36562</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I13" t="n">
-        <v>0.99</v>
+        <v>1.33</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 19:11</t>
+          <t>2025-07-28 19:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.26699</v>
+        <v>0.65505</v>
       </c>
       <c r="E14" t="n">
-        <v>1.26497</v>
+        <v>0.6581399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.27588</v>
+        <v>0.64799</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I14" t="n">
-        <v>4.42</v>
+        <v>2.28</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 19:08</t>
+          <t>2025-07-28 19:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>149.11418</v>
+        <v>1.27183</v>
       </c>
       <c r="E15" t="n">
-        <v>149.31518</v>
+        <v>1.2696</v>
       </c>
       <c r="F15" t="n">
-        <v>148.20714</v>
+        <v>1.28111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>4.51</v>
+        <v>4.15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1463,7 +1547,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 19:52</t>
+          <t>2025-07-28 19:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,26 +1561,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88032</v>
+        <v>0.8793</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87825</v>
+        <v>0.87649</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8867</v>
+        <v>0.88683</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:02</t>
+          <t>2025-07-28 19:22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.88091</v>
+        <v>2334.21327</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.88518</v>
+        <v>2334.21685</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.87119</v>
+        <v>2334.20676</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.27</v>
+        <v>1.82</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,12 +572,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 19:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -586,24 +586,24 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.59179</v>
+        <v>149.85394</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.58828</v>
+        <v>149.37612</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5992</v>
+        <v>150.65947</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.11</v>
+        <v>1.69</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,12 +614,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:53</t>
+          <t>2025-07-28 20:14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,24 +628,24 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>150.15321</v>
+        <v>2330.99258</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>149.91022</v>
+        <v>2330.98966</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>150.6297</v>
+        <v>2331.00069</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:28</t>
+          <t>2025-07-28 20:08</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>XAUEUR</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>148.8192</v>
+        <v>2425.36463</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>149.03316</v>
+        <v>2425.36158</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>148.41725</v>
+        <v>2425.37288</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -698,12 +698,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:02</t>
+          <t>2025-07-28 19:55</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -712,24 +712,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.37045</v>
+        <v>148.85479</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.37409</v>
+        <v>149.12514</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.36562</v>
+        <v>147.95812</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.33</v>
+        <v>3.32</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:17</t>
+          <t>2025-07-28 20:19</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.27183</v>
+        <v>0.88023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.2696</v>
+        <v>0.88297</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.28111</v>
+        <v>0.87613</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.15</v>
+        <v>1.49</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:36</t>
+          <t>2025-07-28 20:01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -796,26 +796,68 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.8793</v>
+        <v>0.66044</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.87649</v>
+        <v>0.65635</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.88683</v>
+        <v>0.66739</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2.68</v>
+        <v>1.7</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 19:56</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2657.19974</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2657.20194</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2657.19485</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>78.0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -859,7 +901,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -890,7 +932,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -902,7 +944,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -914,7 +956,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:45:30</t>
+          <t>2025-07-28 19:51:42</t>
         </is>
       </c>
     </row>
@@ -987,76 +1029,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:02</t>
+          <t>2025-07-28 20:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.88091</v>
+        <v>2639.10754</v>
       </c>
       <c r="E2" t="n">
-        <v>0.88518</v>
+        <v>2639.10473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.87119</v>
+        <v>2639.11523</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2.27</v>
+        <v>2.73</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 19:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.59179</v>
+        <v>2334.21327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58828</v>
+        <v>2334.21685</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5992</v>
+        <v>2334.20676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="I3" t="n">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1067,92 +1109,92 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 19:47</t>
+          <t>2025-07-28 19:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.36364</v>
+        <v>148.7955</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3615</v>
+        <v>149.02496</v>
       </c>
       <c r="F4" t="n">
-        <v>1.37179</v>
+        <v>148.32316</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>3.81</v>
+        <v>2.06</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 19:55</t>
+          <t>2025-07-28 19:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.36515</v>
+        <v>149.85394</v>
       </c>
       <c r="E5" t="n">
-        <v>1.36797</v>
+        <v>149.37612</v>
       </c>
       <c r="F5" t="n">
-        <v>1.36039</v>
+        <v>150.65947</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="I5" t="n">
         <v>1.69</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 19:53</t>
+          <t>2025-07-28 20:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1161,22 +1203,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150.15321</v>
+        <v>2330.99258</v>
       </c>
       <c r="E6" t="n">
-        <v>149.91022</v>
+        <v>2330.98966</v>
       </c>
       <c r="F6" t="n">
-        <v>150.6297</v>
+        <v>2331.00069</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1187,12 +1229,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 19:54</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,102 +1243,102 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.10416</v>
+        <v>0.58889</v>
       </c>
       <c r="E7" t="n">
-        <v>1.10896</v>
+        <v>0.59119</v>
       </c>
       <c r="F7" t="n">
-        <v>1.09589</v>
+        <v>0.58034</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="I7" t="n">
-        <v>1.72</v>
+        <v>3.72</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 19:47</t>
+          <t>2025-07-28 20:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.27152</v>
+        <v>2425.36463</v>
       </c>
       <c r="E8" t="n">
-        <v>1.27443</v>
+        <v>2425.36158</v>
       </c>
       <c r="F8" t="n">
-        <v>1.26464</v>
+        <v>2425.37288</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:56</t>
+          <t>2025-07-28 19:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.36167</v>
+        <v>4032.93353</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36465</v>
+        <v>4032.9298</v>
       </c>
       <c r="F9" t="n">
-        <v>1.35637</v>
+        <v>4032.93825</v>
       </c>
       <c r="G9" t="n">
         <v>0.03</v>
       </c>
       <c r="H9" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="I9" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1307,52 +1349,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:46</t>
+          <t>2025-07-28 19:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.27579</v>
+        <v>149.13696</v>
       </c>
       <c r="E10" t="n">
-        <v>1.27373</v>
+        <v>149.62288</v>
       </c>
       <c r="F10" t="n">
-        <v>1.28514</v>
+        <v>148.65307</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>4.55</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:20</t>
+          <t>2025-07-28 19:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1361,38 +1403,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.88015</v>
+        <v>148.85479</v>
       </c>
       <c r="E11" t="n">
-        <v>0.88296</v>
+        <v>149.12514</v>
       </c>
       <c r="F11" t="n">
-        <v>0.87033</v>
+        <v>147.95812</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 19:28</t>
+          <t>2025-07-28 20:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1401,22 +1443,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>148.8192</v>
+        <v>0.88023</v>
       </c>
       <c r="E12" t="n">
-        <v>149.03316</v>
+        <v>0.88297</v>
       </c>
       <c r="F12" t="n">
-        <v>148.41725</v>
+        <v>0.87613</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H12" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1427,36 +1469,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:02</t>
+          <t>2025-07-28 20:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.37045</v>
+        <v>0.66044</v>
       </c>
       <c r="E13" t="n">
-        <v>1.37409</v>
+        <v>0.65635</v>
       </c>
       <c r="F13" t="n">
-        <v>1.36562</v>
+        <v>0.66739</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H13" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1467,12 +1509,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 19:53</t>
+          <t>2025-07-28 20:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1481,33 +1523,33 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.65505</v>
+        <v>2412.71651</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6581399999999999</v>
+        <v>2412.71944</v>
       </c>
       <c r="F14" t="n">
-        <v>0.64799</v>
+        <v>2412.71005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 19:17</t>
+          <t>2025-07-28 19:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1517,66 +1559,66 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.27183</v>
+        <v>1.26529</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2696</v>
+        <v>1.26994</v>
       </c>
       <c r="F15" t="n">
-        <v>1.28111</v>
+        <v>1.25782</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="I15" t="n">
-        <v>4.15</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 19:36</t>
+          <t>2025-07-28 19:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.8793</v>
+        <v>2657.19974</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87649</v>
+        <v>2657.20194</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88683</v>
+        <v>2657.19485</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,38 +530,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:22</t>
+          <t>2025-07-28 20:18</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2334.21327</v>
+        <v>1.10095</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2334.21685</v>
+        <v>1.09751</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2334.20676</v>
+        <v>1.10812</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,292 +572,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:57</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>149.85394</v>
+        <v>2646.76589</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>149.37612</v>
+        <v>2646.76804</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>150.65947</v>
+        <v>2646.75787</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.69</v>
+        <v>3.73</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:14</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>XAUCHF</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2330.99258</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2330.98966</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2331.00069</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87.0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>XAUEUR</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2425.36463</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2425.36158</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2425.37288</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85.0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 19:55</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>USDJPY</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>148.85479</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>149.12514</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>147.95812</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>88.0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:19</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>USDCHF</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.88023</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.88297</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.87613</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>AUDUSD</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.66044</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.65635</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.66739</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81.0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 19:56</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>2657.19974</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>2657.20194</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>2657.19485</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>78.0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -901,7 +649,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -911,7 +659,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -921,7 +669,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -932,7 +680,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -944,7 +692,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.29</t>
         </is>
       </c>
     </row>
@@ -956,7 +704,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:51:42</t>
+          <t>2025-07-28 19:56:12</t>
         </is>
       </c>
     </row>
@@ -1029,12 +777,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:07</t>
+          <t>2025-07-28 19:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,38 +791,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2639.10754</v>
+        <v>1.10417</v>
       </c>
       <c r="E2" t="n">
-        <v>2639.10473</v>
+        <v>1.09996</v>
       </c>
       <c r="F2" t="n">
-        <v>2639.11523</v>
+        <v>1.11413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="I2" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 19:22</t>
+          <t>2025-07-28 19:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1083,38 +831,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2334.21327</v>
+        <v>150.17889</v>
       </c>
       <c r="E3" t="n">
-        <v>2334.21685</v>
+        <v>150.67464</v>
       </c>
       <c r="F3" t="n">
-        <v>2334.20676</v>
+        <v>149.39819</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 19:43</t>
+          <t>2025-07-28 20:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1123,33 +871,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>148.7955</v>
+        <v>2105.81156</v>
       </c>
       <c r="E4" t="n">
-        <v>149.02496</v>
+        <v>2105.81421</v>
       </c>
       <c r="F4" t="n">
-        <v>148.32316</v>
+        <v>2105.80399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>2.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 19:57</t>
+          <t>2025-07-28 20:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1163,33 +911,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>149.85394</v>
+        <v>150.23958</v>
       </c>
       <c r="E5" t="n">
-        <v>149.37612</v>
+        <v>150.00475</v>
       </c>
       <c r="F5" t="n">
-        <v>150.65947</v>
+        <v>150.65111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 20:14</t>
+          <t>2025-07-28 19:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1203,38 +951,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2330.99258</v>
+        <v>2345.83131</v>
       </c>
       <c r="E6" t="n">
-        <v>2330.98966</v>
+        <v>2345.82699</v>
       </c>
       <c r="F6" t="n">
-        <v>2331.00069</v>
+        <v>2345.83617</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>2.78</v>
+        <v>1.12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 19:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,22 +991,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58889</v>
+        <v>1.10132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.59119</v>
+        <v>1.10507</v>
       </c>
       <c r="F7" t="n">
-        <v>0.58034</v>
+        <v>1.09573</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.72</v>
+        <v>1.49</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1269,12 +1017,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:08</t>
+          <t>2025-07-28 20:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1283,22 +1031,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2425.36463</v>
+        <v>1.10095</v>
       </c>
       <c r="E8" t="n">
-        <v>2425.36158</v>
+        <v>1.09751</v>
       </c>
       <c r="F8" t="n">
-        <v>2425.37288</v>
+        <v>1.10812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1309,36 +1057,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:39</t>
+          <t>2025-07-28 19:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4032.93353</v>
+        <v>2093.56937</v>
       </c>
       <c r="E9" t="n">
-        <v>4032.9298</v>
+        <v>2093.57231</v>
       </c>
       <c r="F9" t="n">
-        <v>4032.93825</v>
+        <v>2093.5647</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1349,172 +1097,172 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:47</t>
+          <t>2025-07-28 19:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>149.13696</v>
+        <v>0.59234</v>
       </c>
       <c r="E10" t="n">
-        <v>149.62288</v>
+        <v>0.58994</v>
       </c>
       <c r="F10" t="n">
-        <v>148.65307</v>
+        <v>0.60129</v>
       </c>
       <c r="G10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3.74</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:55</t>
+          <t>2025-07-28 19:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>148.85479</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>149.12514</v>
+        <v>0.58645</v>
       </c>
       <c r="F11" t="n">
-        <v>147.95812</v>
+        <v>0.59809</v>
       </c>
       <c r="G11" t="n">
         <v>0.08</v>
       </c>
       <c r="H11" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="I11" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:19</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.88023</v>
+        <v>3602.70636</v>
       </c>
       <c r="E12" t="n">
-        <v>0.88297</v>
+        <v>3602.70329</v>
       </c>
       <c r="F12" t="n">
-        <v>0.87613</v>
+        <v>3602.71461</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.49</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:01</t>
+          <t>2025-07-28 20:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.66044</v>
+        <v>0.87935</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65635</v>
+        <v>0.8829900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.66739</v>
+        <v>0.87307</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 20:01</t>
+          <t>2025-07-28 19:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1523,22 +1271,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412.71651</v>
+        <v>2341.82489</v>
       </c>
       <c r="E14" t="n">
-        <v>2412.71944</v>
+        <v>2341.82898</v>
       </c>
       <c r="F14" t="n">
-        <v>2412.71005</v>
+        <v>2341.81819</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="I14" t="n">
-        <v>2.21</v>
+        <v>1.64</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1549,36 +1297,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 19:25</t>
+          <t>2025-07-28 20:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.26529</v>
+        <v>0.88243</v>
       </c>
       <c r="E15" t="n">
-        <v>1.26994</v>
+        <v>0.8788899999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.25782</v>
+        <v>0.89208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>0.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2.73</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1589,7 +1337,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 19:56</t>
+          <t>2025-07-28 20:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1603,22 +1351,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2657.19974</v>
+        <v>2646.76589</v>
       </c>
       <c r="E16" t="n">
-        <v>2657.20194</v>
+        <v>2646.76804</v>
       </c>
       <c r="F16" t="n">
-        <v>2657.19485</v>
+        <v>2646.75787</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>2.23</v>
+        <v>3.73</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:18</t>
+          <t>2025-07-28 20:03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.10095</v>
+        <v>2334.28355</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.09751</v>
+        <v>2334.27912</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.10812</v>
+        <v>2334.29131</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,40 +572,166 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 19:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.59221</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.58799</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.59656</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>76.0%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 19:43</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>2646.76589</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2646.76804</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2646.75787</v>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="D4" s="2" t="n">
+        <v>2336.548</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2336.55109</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2336.54131</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>76.0%</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 20:08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>149.07482</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>149.36232</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>148.34779</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 20:24</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>149.10511</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>148.847</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>150.01508</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>81.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -649,7 +775,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -680,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -692,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -704,7 +830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:56:12</t>
+          <t>2025-07-28 20:00:31</t>
         </is>
       </c>
     </row>
@@ -777,12 +903,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:57</t>
+          <t>2025-07-28 20:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -791,38 +917,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.10417</v>
+        <v>149.43539</v>
       </c>
       <c r="E2" t="n">
-        <v>1.09996</v>
+        <v>149.15827</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11413</v>
+        <v>150.33336</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H2" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="I2" t="n">
-        <v>2.36</v>
+        <v>3.24</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 19:27</t>
+          <t>2025-07-28 20:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -831,22 +957,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150.17889</v>
+        <v>2105.39076</v>
       </c>
       <c r="E3" t="n">
-        <v>150.67464</v>
+        <v>2105.39337</v>
       </c>
       <c r="F3" t="n">
-        <v>149.39819</v>
+        <v>2105.38149</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.57</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -857,52 +983,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:06</t>
+          <t>2025-07-28 20:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2105.81156</v>
+        <v>2334.28355</v>
       </c>
       <c r="E4" t="n">
-        <v>2105.81421</v>
+        <v>2334.27912</v>
       </c>
       <c r="F4" t="n">
-        <v>2105.80399</v>
+        <v>2334.29131</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:00</t>
+          <t>2025-07-28 19:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -911,38 +1037,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>150.23958</v>
+        <v>0.59221</v>
       </c>
       <c r="E5" t="n">
-        <v>150.00475</v>
+        <v>0.58799</v>
       </c>
       <c r="F5" t="n">
-        <v>150.65111</v>
+        <v>0.59656</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 19:52</t>
+          <t>2025-07-28 20:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,22 +1077,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2345.83131</v>
+        <v>4068.58247</v>
       </c>
       <c r="E6" t="n">
-        <v>2345.82699</v>
+        <v>4068.57785</v>
       </c>
       <c r="F6" t="n">
-        <v>2345.83617</v>
+        <v>4068.5889</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -977,12 +1103,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 19:34</t>
+          <t>2025-07-28 19:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -991,33 +1117,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.10132</v>
+        <v>2336.548</v>
       </c>
       <c r="E7" t="n">
-        <v>1.10507</v>
+        <v>2336.55109</v>
       </c>
       <c r="F7" t="n">
-        <v>1.09573</v>
+        <v>2336.54131</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="I7" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:18</t>
+          <t>2025-07-28 19:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1031,73 +1157,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.10095</v>
+        <v>1.10507</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09751</v>
+        <v>1.1005</v>
       </c>
       <c r="F8" t="n">
-        <v>1.10812</v>
+        <v>1.10936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>2.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 19:50</t>
+          <t>2025-07-28 20:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2093.56937</v>
+        <v>2644.48224</v>
       </c>
       <c r="E9" t="n">
-        <v>2093.57231</v>
+        <v>2644.47753</v>
       </c>
       <c r="F9" t="n">
-        <v>2093.5647</v>
+        <v>2644.48859</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="I9" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:42</t>
+          <t>2025-07-28 19:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1107,26 +1233,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.59234</v>
+        <v>0.58648</v>
       </c>
       <c r="E10" t="n">
-        <v>0.58994</v>
+        <v>0.58863</v>
       </c>
       <c r="F10" t="n">
-        <v>0.60129</v>
+        <v>0.58035</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1137,76 +1263,76 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:30</t>
+          <t>2025-07-28 20:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5891999999999999</v>
+        <v>149.07482</v>
       </c>
       <c r="E11" t="n">
-        <v>0.58645</v>
+        <v>149.36232</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59809</v>
+        <v>148.34779</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H11" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>3.24</v>
+        <v>2.53</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 20:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3602.70636</v>
+        <v>1.36369</v>
       </c>
       <c r="E12" t="n">
-        <v>3602.70329</v>
+        <v>1.36737</v>
       </c>
       <c r="F12" t="n">
-        <v>3602.71461</v>
+        <v>1.35429</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1217,52 +1343,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:03</t>
+          <t>2025-07-28 20:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.87935</v>
+        <v>149.10511</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8829900000000001</v>
+        <v>148.847</v>
       </c>
       <c r="F13" t="n">
-        <v>0.87307</v>
+        <v>150.01508</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.72</v>
+        <v>3.53</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 19:30</t>
+          <t>2025-07-28 19:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1271,62 +1397,62 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2341.82489</v>
+        <v>2422.95788</v>
       </c>
       <c r="E14" t="n">
-        <v>2341.82898</v>
+        <v>2422.96252</v>
       </c>
       <c r="F14" t="n">
-        <v>2341.81819</v>
+        <v>2422.95307</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="I14" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 20:13</t>
+          <t>2025-07-28 19:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.88243</v>
+        <v>2649.17888</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8788899999999999</v>
+        <v>2649.18361</v>
       </c>
       <c r="F15" t="n">
-        <v>0.89208</v>
+        <v>2649.17293</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1337,40 +1463,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 20:04</t>
+          <t>2025-07-28 20:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2646.76589</v>
+        <v>0.88436</v>
       </c>
       <c r="E16" t="n">
-        <v>2646.76804</v>
+        <v>0.87957</v>
       </c>
       <c r="F16" t="n">
-        <v>2646.75787</v>
+        <v>0.89366</v>
       </c>
       <c r="G16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.73</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,30 +530,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:03</t>
+          <t>2025-07-28 20:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2334.28355</v>
+        <v>2093.51867</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2334.27912</v>
+        <v>2093.52187</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2334.29131</v>
+        <v>2093.5146</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:51</t>
+          <t>2025-07-28 20:33</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.59221</v>
+        <v>3637.02642</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.58799</v>
+        <v>3637.02962</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.59656</v>
+        <v>3637.02181</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 19:43</t>
+          <t>2025-07-28 20:05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2336.548</v>
+        <v>1.36249</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2336.55109</v>
+        <v>1.35919</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2336.54131</v>
+        <v>1.37219</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.16</v>
+        <v>2.94</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:08</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>149.07482</v>
+        <v>2338.51219</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>149.36232</v>
+        <v>2338.50814</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>148.34779</v>
+        <v>2338.52196</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -698,38 +698,38 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:24</t>
+          <t>2025-07-28 20:39</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+          <t>XAUEUR</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>149.10511</v>
+        <v>2413.91887</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>148.847</v>
+        <v>2413.91527</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>150.01508</v>
+        <v>2413.92515</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3.53</v>
+        <v>1.74</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:00:31</t>
+          <t>2025-07-28 20:23:57</t>
         </is>
       </c>
     </row>
@@ -903,52 +903,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:10</t>
+          <t>2025-07-28 20:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>149.43539</v>
+        <v>2093.51867</v>
       </c>
       <c r="E2" t="n">
-        <v>149.15827</v>
+        <v>2093.52187</v>
       </c>
       <c r="F2" t="n">
-        <v>150.33336</v>
+        <v>2093.5146</v>
       </c>
       <c r="G2" t="n">
         <v>0.04</v>
       </c>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.24</v>
+        <v>1.27</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:10</t>
+          <t>2025-07-28 20:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2105.39076</v>
+        <v>2418.08605</v>
       </c>
       <c r="E3" t="n">
-        <v>2105.39337</v>
+        <v>2418.09006</v>
       </c>
       <c r="F3" t="n">
-        <v>2105.38149</v>
+        <v>2418.0814</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>1.16</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -983,36 +983,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:03</t>
+          <t>2025-07-28 20:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2334.28355</v>
+        <v>3637.02642</v>
       </c>
       <c r="E4" t="n">
-        <v>2334.27912</v>
+        <v>3637.02962</v>
       </c>
       <c r="F4" t="n">
-        <v>2334.29131</v>
+        <v>3637.02181</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1023,12 +1023,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 19:51</t>
+          <t>2025-07-28 20:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1037,38 +1037,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.59221</v>
+        <v>0.8848</v>
       </c>
       <c r="E5" t="n">
-        <v>0.58799</v>
+        <v>0.88062</v>
       </c>
       <c r="F5" t="n">
-        <v>0.59656</v>
+        <v>0.89168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 20:01</t>
+          <t>2025-07-28 20:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1077,118 +1077,118 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4068.58247</v>
+        <v>1.36249</v>
       </c>
       <c r="E6" t="n">
-        <v>4068.57785</v>
+        <v>1.35919</v>
       </c>
       <c r="F6" t="n">
-        <v>4068.5889</v>
+        <v>1.37219</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H6" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>1.39</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 19:43</t>
+          <t>2025-07-28 20:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2336.548</v>
+        <v>149.94536</v>
       </c>
       <c r="E7" t="n">
-        <v>2336.55109</v>
+        <v>149.5977</v>
       </c>
       <c r="F7" t="n">
-        <v>2336.54131</v>
+        <v>150.9003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 19:41</t>
+          <t>2025-07-28 20:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.10507</v>
+        <v>0.87869</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1005</v>
+        <v>0.88166</v>
       </c>
       <c r="F8" t="n">
-        <v>1.10936</v>
+        <v>0.8714499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H8" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:19</t>
+          <t>2025-07-28 20:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1197,38 +1197,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2644.48224</v>
+        <v>2107.12619</v>
       </c>
       <c r="E9" t="n">
-        <v>2644.47753</v>
+        <v>2107.1232</v>
       </c>
       <c r="F9" t="n">
-        <v>2644.48859</v>
+        <v>2107.13299</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 19:44</t>
+          <t>2025-07-28 20:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1237,22 +1237,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.58648</v>
+        <v>2416.53418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.58863</v>
+        <v>2416.5373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.58035</v>
+        <v>2416.53013</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.85</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1263,36 +1263,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:08</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>149.07482</v>
+        <v>2338.51219</v>
       </c>
       <c r="E11" t="n">
-        <v>149.36232</v>
+        <v>2338.50814</v>
       </c>
       <c r="F11" t="n">
-        <v>148.34779</v>
+        <v>2338.52196</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:25</t>
+          <t>2025-07-28 19:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1317,22 +1317,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.36369</v>
+        <v>0.65846</v>
       </c>
       <c r="E12" t="n">
-        <v>1.36737</v>
+        <v>0.66216</v>
       </c>
       <c r="F12" t="n">
-        <v>1.35429</v>
+        <v>0.6499</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H12" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1343,12 +1343,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:24</t>
+          <t>2025-07-28 20:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1357,38 +1357,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>149.10511</v>
+        <v>2417.12925</v>
       </c>
       <c r="E13" t="n">
-        <v>148.847</v>
+        <v>2417.12517</v>
       </c>
       <c r="F13" t="n">
-        <v>150.01508</v>
+        <v>2417.13821</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>3.53</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 19:51</t>
+          <t>2025-07-28 20:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1397,56 +1397,56 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2422.95788</v>
+        <v>2661.95755</v>
       </c>
       <c r="E14" t="n">
-        <v>2422.96252</v>
+        <v>2661.95969</v>
       </c>
       <c r="F14" t="n">
-        <v>2422.95307</v>
+        <v>2661.95199</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H14" t="n">
         <v>0.84</v>
       </c>
       <c r="I14" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 19:57</t>
+          <t>2025-07-28 20:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2649.17888</v>
+        <v>2348.2017</v>
       </c>
       <c r="E15" t="n">
-        <v>2649.18361</v>
+        <v>2348.19708</v>
       </c>
       <c r="F15" t="n">
-        <v>2649.17293</v>
+        <v>2348.20753</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H15" t="n">
         <v>0.78</v>
@@ -1456,19 +1456,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 20:21</t>
+          <t>2025-07-28 20:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1477,26 +1477,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88436</v>
+        <v>2413.91887</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87957</v>
+        <v>2413.91527</v>
       </c>
       <c r="F16" t="n">
-        <v>0.89366</v>
+        <v>2413.92515</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,38 +530,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:09</t>
+          <t>2025-07-28 21:03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2093.51867</v>
+        <v>1.10695</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2093.52187</v>
+        <v>1.10383</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2093.5146</v>
+        <v>1.11219</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:33</t>
+          <t>2025-07-28 21:16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3637.02642</v>
+        <v>0.87879</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3637.02962</v>
+        <v>0.88296</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3637.02181</v>
+        <v>0.87072</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,124 +614,40 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:05</t>
+          <t>2025-07-28 20:40</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDCAD</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.36249</v>
+        <v>0.87926</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.35919</v>
+        <v>0.87699</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.37219</v>
+        <v>0.8847</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 19:54</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>XAUCHF</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2338.51219</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2338.50814</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2338.52196</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88.0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:39</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>XAUEUR</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2413.91887</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>2413.91527</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2413.92515</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>83.0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -775,7 +691,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -785,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -795,7 +711,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -806,7 +722,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>85.8%</t>
         </is>
       </c>
     </row>
@@ -818,7 +734,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.14</t>
         </is>
       </c>
     </row>
@@ -830,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:23:57</t>
+          <t>2025-07-28 20:56:28</t>
         </is>
       </c>
     </row>
@@ -903,36 +819,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:09</t>
+          <t>2025-07-28 21:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2093.51867</v>
+        <v>1.10695</v>
       </c>
       <c r="E2" t="n">
-        <v>2093.52187</v>
+        <v>1.10383</v>
       </c>
       <c r="F2" t="n">
-        <v>2093.5146</v>
+        <v>1.11219</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -943,12 +859,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:44</t>
+          <t>2025-07-28 20:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -957,78 +873,78 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2418.08605</v>
+        <v>0.88184</v>
       </c>
       <c r="E3" t="n">
-        <v>2418.09006</v>
+        <v>0.8858</v>
       </c>
       <c r="F3" t="n">
-        <v>2418.0814</v>
+        <v>0.8768899999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="n">
         <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:33</t>
+          <t>2025-07-28 20:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3637.02642</v>
+        <v>1.10663</v>
       </c>
       <c r="E4" t="n">
-        <v>3637.02962</v>
+        <v>1.10299</v>
       </c>
       <c r="F4" t="n">
-        <v>3637.02181</v>
+        <v>1.11359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:09</t>
+          <t>2025-07-28 21:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1037,22 +953,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8848</v>
+        <v>149.23577</v>
       </c>
       <c r="E5" t="n">
-        <v>0.88062</v>
+        <v>149.00513</v>
       </c>
       <c r="F5" t="n">
-        <v>0.89168</v>
+        <v>149.6558</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1063,92 +979,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 20:05</t>
+          <t>2025-07-28 20:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.36249</v>
+        <v>4065.77924</v>
       </c>
       <c r="E6" t="n">
-        <v>1.35919</v>
+        <v>4065.78308</v>
       </c>
       <c r="F6" t="n">
-        <v>1.37219</v>
+        <v>4065.77082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>2.19</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:44</t>
+          <t>2025-07-28 21:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>149.94536</v>
+        <v>2344.45541</v>
       </c>
       <c r="E7" t="n">
-        <v>149.5977</v>
+        <v>2344.45954</v>
       </c>
       <c r="F7" t="n">
-        <v>150.9003</v>
+        <v>2344.44827</v>
       </c>
       <c r="G7" t="n">
         <v>0.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="I7" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:42</t>
+          <t>2025-07-28 21:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1157,22 +1073,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.87869</v>
+        <v>1.10121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.88166</v>
+        <v>1.10352</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8714499999999999</v>
+        <v>1.09431</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1183,52 +1099,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:50</t>
+          <t>2025-07-28 21:16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2107.12619</v>
+        <v>0.87879</v>
       </c>
       <c r="E9" t="n">
-        <v>2107.1232</v>
+        <v>0.88296</v>
       </c>
       <c r="F9" t="n">
-        <v>2107.13299</v>
+        <v>0.87072</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H9" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 20:24</t>
+          <t>2025-07-28 21:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1237,22 +1153,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2416.53418</v>
+        <v>2640.34649</v>
       </c>
       <c r="E10" t="n">
-        <v>2416.5373</v>
+        <v>2640.34899</v>
       </c>
       <c r="F10" t="n">
-        <v>2416.53013</v>
+        <v>2640.33792</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>3.41</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1263,12 +1179,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 19:54</t>
+          <t>2025-07-28 20:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1277,22 +1193,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2338.51219</v>
+        <v>0.87926</v>
       </c>
       <c r="E11" t="n">
-        <v>2338.50814</v>
+        <v>0.87699</v>
       </c>
       <c r="F11" t="n">
-        <v>2338.52196</v>
+        <v>0.8847</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H11" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1303,7 +1219,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 19:54</t>
+          <t>2025-07-28 20:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,22 +1233,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.65846</v>
+        <v>0.65717</v>
       </c>
       <c r="E12" t="n">
-        <v>0.66216</v>
+        <v>0.66009</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6499</v>
+        <v>0.6475</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="I12" t="n">
-        <v>2.32</v>
+        <v>3.31</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1343,52 +1259,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:33</t>
+          <t>2025-07-28 21:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2417.12925</v>
+        <v>1.10421</v>
       </c>
       <c r="E13" t="n">
-        <v>2417.12517</v>
+        <v>1.10631</v>
       </c>
       <c r="F13" t="n">
-        <v>2417.13821</v>
+        <v>1.09805</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H13" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 20:29</t>
+          <t>2025-07-28 21:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1397,62 +1313,62 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2661.95755</v>
+        <v>1.36718</v>
       </c>
       <c r="E14" t="n">
-        <v>2661.95969</v>
+        <v>1.3706</v>
       </c>
       <c r="F14" t="n">
-        <v>2661.95199</v>
+        <v>1.36273</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H14" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 20:12</t>
+          <t>2025-07-28 21:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2348.2017</v>
+        <v>0.58909</v>
       </c>
       <c r="E15" t="n">
-        <v>2348.19708</v>
+        <v>0.5918</v>
       </c>
       <c r="F15" t="n">
-        <v>2348.20753</v>
+        <v>0.5845</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H15" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1463,12 +1379,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 20:39</t>
+          <t>2025-07-28 20:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1477,26 +1393,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2413.91887</v>
+        <v>1.27296</v>
       </c>
       <c r="E16" t="n">
-        <v>2413.91527</v>
+        <v>1.26797</v>
       </c>
       <c r="F16" t="n">
-        <v>2413.92515</v>
+        <v>1.28042</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H16" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="I16" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,14 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -460,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:03</t>
+          <t>2025-07-28 21:20</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +537,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.10695</v>
+        <v>4050.075</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.10383</v>
+        <v>4050.07069</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.11219</v>
+        <v>4050.07993</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +565,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:16</t>
+          <t>2025-07-28 21:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>XAUCAD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.87879</v>
+        <v>3612.73645</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.88296</v>
+        <v>3612.73385</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.87072</v>
+        <v>3612.74238</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,12 +607,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2025-07-28 20:46</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -628,26 +621,152 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.87926</v>
+        <v>2409.80569</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.87699</v>
+        <v>2409.8021</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8847</v>
+        <v>2409.81324</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 21:06</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>XAUEUR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2430.46354</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2430.4592</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2430.46898</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 20:58</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2658.28655</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2658.28254</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2658.29248</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28 21:28</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2342.20274</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2342.19957</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2342.21077</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -668,14 +787,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -685,68 +804,68 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:56:28</t>
+          <t>2025-07-28 21:05:50</t>
         </is>
       </c>
     </row>
@@ -765,52 +884,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -819,92 +938,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:03</t>
+          <t>2025-07-28 21:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.10695</v>
+        <v>0.87883</v>
       </c>
       <c r="E2" t="n">
-        <v>1.10383</v>
+        <v>0.88343</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11219</v>
+        <v>0.87402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.68</v>
+        <v>1.05</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:53</t>
+          <t>2025-07-28 21:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.88184</v>
+        <v>4050.075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8858</v>
+        <v>4050.07069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8768899999999999</v>
+        <v>4050.07993</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:32</t>
+          <t>2025-07-28 21:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -913,38 +1032,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10663</v>
+        <v>3612.73645</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10299</v>
+        <v>3612.73385</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11359</v>
+        <v>3612.74238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 21:13</t>
+          <t>2025-07-28 20:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -953,22 +1072,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>149.23577</v>
+        <v>2347.84751</v>
       </c>
       <c r="E5" t="n">
-        <v>149.00513</v>
+        <v>2347.84358</v>
       </c>
       <c r="F5" t="n">
-        <v>149.6558</v>
+        <v>2347.85424</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -979,12 +1098,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 20:30</t>
+          <t>2025-07-28 21:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -993,113 +1112,113 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4065.77924</v>
+        <v>1.36148</v>
       </c>
       <c r="E6" t="n">
-        <v>4065.78308</v>
+        <v>1.36404</v>
       </c>
       <c r="F6" t="n">
-        <v>4065.77082</v>
+        <v>1.35459</v>
       </c>
       <c r="G6" t="n">
         <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.19</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 21:03</t>
+          <t>2025-07-28 20:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2344.45541</v>
+        <v>2409.80569</v>
       </c>
       <c r="E7" t="n">
-        <v>2344.45954</v>
+        <v>2409.8021</v>
       </c>
       <c r="F7" t="n">
-        <v>2344.44827</v>
+        <v>2409.81324</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 21:12</t>
+          <t>2025-07-28 21:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.10121</v>
+        <v>0.6583</v>
       </c>
       <c r="E8" t="n">
-        <v>1.10352</v>
+        <v>0.65416</v>
       </c>
       <c r="F8" t="n">
-        <v>1.09431</v>
+        <v>0.66778</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:16</t>
+          <t>2025-07-28 20:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1113,118 +1232,118 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.87879</v>
+        <v>0.8781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.88296</v>
+        <v>0.8825</v>
       </c>
       <c r="F9" t="n">
-        <v>0.87072</v>
+        <v>0.87026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:25</t>
+          <t>2025-07-28 21:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2640.34649</v>
+        <v>2430.46354</v>
       </c>
       <c r="E10" t="n">
-        <v>2640.34899</v>
+        <v>2430.4592</v>
       </c>
       <c r="F10" t="n">
-        <v>2640.33792</v>
+        <v>2430.46898</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3.41</v>
+        <v>1.25</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2025-07-28 20:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.87926</v>
+        <v>1.09942</v>
       </c>
       <c r="E11" t="n">
-        <v>0.87699</v>
+        <v>1.10151</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8847</v>
+        <v>1.09073</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>4.17</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:28</t>
+          <t>2025-07-28 21:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1233,22 +1352,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.65717</v>
+        <v>3612.22436</v>
       </c>
       <c r="E12" t="n">
-        <v>0.66009</v>
+        <v>3612.22808</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6475</v>
+        <v>3612.21709</v>
       </c>
       <c r="G12" t="n">
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="n">
-        <v>3.31</v>
+        <v>1.96</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1259,52 +1378,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 21:26</t>
+          <t>2025-07-28 20:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10421</v>
+        <v>2658.28655</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10631</v>
+        <v>2658.28254</v>
       </c>
       <c r="F13" t="n">
-        <v>1.09805</v>
+        <v>2658.29248</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>2.93</v>
+        <v>1.48</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 21:09</t>
+          <t>2025-07-28 20:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1313,22 +1432,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.36718</v>
+        <v>0.65913</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3706</v>
+        <v>0.66182</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36273</v>
+        <v>0.65303</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.27</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1339,12 +1458,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 21:13</t>
+          <t>2025-07-28 20:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1353,38 +1472,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.58909</v>
+        <v>2412.69942</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5918</v>
+        <v>2412.70367</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5845</v>
+        <v>2412.68955</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H15" t="n">
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>1.69</v>
+        <v>2.32</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 20:41</t>
+          <t>2025-07-28 21:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1393,26 +1512,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.27296</v>
+        <v>2342.20274</v>
       </c>
       <c r="E16" t="n">
-        <v>1.26797</v>
+        <v>2342.19957</v>
       </c>
       <c r="F16" t="n">
-        <v>1.28042</v>
+        <v>2342.21077</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.53</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,13 +84,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -523,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:20</t>
+          <t>2025-07-28 21:28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -537,20 +544,20 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4050.075</v>
+        <v>4064.91481</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4050.07069</v>
+        <v>4064.91121</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4050.07993</v>
+        <v>4064.91896</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -565,208 +572,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:34</t>
+          <t>2025-07-28 20:55</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>XAUGBP</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3612.73645</v>
+        <v>2109.70362</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3612.73385</v>
+        <v>2109.7061</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3612.74238</v>
+        <v>2109.69605</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.29</v>
+        <v>3.04</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:46</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>XAUEUR</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2409.80569</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2409.8021</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2409.81324</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82.0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 21:06</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>XAUEUR</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2430.46354</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2430.4592</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2430.46898</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82.0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 20:58</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2658.28655</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>2658.28254</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2658.29248</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>85.0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-28 21:28</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>XAUCHF</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2342.20274</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>2342.19957</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2342.21077</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88.0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -787,14 +626,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -804,68 +643,68 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>SELL Signals</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SELL Signals</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:05:50</t>
+          <t>2025-07-28 21:07:35</t>
         </is>
       </c>
     </row>
@@ -884,52 +723,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -938,156 +777,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:12</t>
+          <t>2025-07-28 21:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.87883</v>
+        <v>2638.81797</v>
       </c>
       <c r="E2" t="n">
-        <v>0.88343</v>
+        <v>2638.81536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.87402</v>
+        <v>2638.82472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="I2" t="n">
-        <v>1.05</v>
+        <v>2.59</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 21:20</t>
+          <t>2025-07-28 20:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4050.075</v>
+        <v>0.5863</v>
       </c>
       <c r="E3" t="n">
-        <v>4050.07069</v>
+        <v>0.58862</v>
       </c>
       <c r="F3" t="n">
-        <v>4050.07993</v>
+        <v>0.58136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>1.15</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 21:34</t>
+          <t>2025-07-28 20:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3612.73645</v>
+        <v>1.10395</v>
       </c>
       <c r="E4" t="n">
-        <v>3612.73385</v>
+        <v>1.10659</v>
       </c>
       <c r="F4" t="n">
-        <v>3612.74238</v>
+        <v>1.09987</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="I4" t="n">
-        <v>2.29</v>
+        <v>1.54</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:50</t>
+          <t>2025-07-28 20:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2347.84751</v>
+        <v>3602.6381</v>
       </c>
       <c r="E5" t="n">
-        <v>2347.84358</v>
+        <v>3602.64162</v>
       </c>
       <c r="F5" t="n">
-        <v>2347.85424</v>
+        <v>3602.63223</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1098,76 +937,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 21:09</t>
+          <t>2025-07-28 21:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.36148</v>
+        <v>4064.91481</v>
       </c>
       <c r="E6" t="n">
-        <v>1.36404</v>
+        <v>4064.91121</v>
       </c>
       <c r="F6" t="n">
-        <v>1.35459</v>
+        <v>4064.91896</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>2.68</v>
+        <v>1.15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:46</t>
+          <t>2025-07-28 20:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2409.80569</v>
+        <v>2109.70362</v>
       </c>
       <c r="E7" t="n">
-        <v>2409.8021</v>
+        <v>2109.7061</v>
       </c>
       <c r="F7" t="n">
-        <v>2409.81324</v>
+        <v>2109.69605</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>2.11</v>
+        <v>3.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1178,12 +1017,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 21:05</t>
+          <t>2025-07-28 20:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1192,22 +1031,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6583</v>
+        <v>3637.04486</v>
       </c>
       <c r="E8" t="n">
-        <v>0.65416</v>
+        <v>3637.0413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.66778</v>
+        <v>3637.05461</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1218,12 +1057,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 20:46</t>
+          <t>2025-07-28 21:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1232,38 +1071,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8781</v>
+        <v>2330.19431</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8825</v>
+        <v>2330.19843</v>
       </c>
       <c r="F9" t="n">
-        <v>0.87026</v>
+        <v>2330.18961</v>
       </c>
       <c r="G9" t="n">
         <v>0.09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:06</t>
+          <t>2025-07-28 21:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1272,38 +1111,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2430.46354</v>
+        <v>2654.13881</v>
       </c>
       <c r="E10" t="n">
-        <v>2430.4592</v>
+        <v>2654.13442</v>
       </c>
       <c r="F10" t="n">
-        <v>2430.46898</v>
+        <v>2654.14534</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:46</t>
+          <t>2025-07-28 20:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1312,38 +1151,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.09942</v>
+        <v>2414.83832</v>
       </c>
       <c r="E11" t="n">
-        <v>1.10151</v>
+        <v>2414.84059</v>
       </c>
       <c r="F11" t="n">
-        <v>1.09073</v>
+        <v>2414.82938</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H11" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>4.17</v>
+        <v>3.94</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 21:00</t>
+          <t>2025-07-28 20:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1352,38 +1191,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3612.22436</v>
+        <v>0.58938</v>
       </c>
       <c r="E12" t="n">
-        <v>3612.22808</v>
+        <v>0.59428</v>
       </c>
       <c r="F12" t="n">
-        <v>3612.21709</v>
+        <v>0.58413</v>
       </c>
       <c r="G12" t="n">
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>1.96</v>
+        <v>1.07</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 20:58</t>
+          <t>2025-07-28 21:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,78 +1231,78 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2658.28655</v>
+        <v>1.10743</v>
       </c>
       <c r="E13" t="n">
-        <v>2658.28254</v>
+        <v>1.10362</v>
       </c>
       <c r="F13" t="n">
-        <v>2658.29248</v>
+        <v>1.1122</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="I13" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 20:58</t>
+          <t>2025-07-28 21:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.65913</v>
+        <v>2412.942</v>
       </c>
       <c r="E14" t="n">
-        <v>0.66182</v>
+        <v>2412.93763</v>
       </c>
       <c r="F14" t="n">
-        <v>0.65303</v>
+        <v>2412.94933</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 20:49</t>
+          <t>2025-07-28 21:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1472,38 +1311,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2412.69942</v>
+        <v>1.3615</v>
       </c>
       <c r="E15" t="n">
-        <v>2412.70367</v>
+        <v>1.36633</v>
       </c>
       <c r="F15" t="n">
-        <v>2412.68955</v>
+        <v>1.35425</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2025-07-28 21:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1512,26 +1351,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2342.20274</v>
+        <v>0.88156</v>
       </c>
       <c r="E16" t="n">
-        <v>2342.19957</v>
+        <v>0.87934</v>
       </c>
       <c r="F16" t="n">
-        <v>2342.21077</v>
+        <v>0.88597</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H16" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,12 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,14 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -460,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,38 +523,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-16 16:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4064.91481</v>
+        <v>0.58709</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4064.91121</v>
+        <v>0.58994</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4064.91896</v>
+        <v>0.58014</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,40 +565,82 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-16 16:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2109.70362</v>
+        <v>2335.0146</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2109.7061</v>
+        <v>2335.01789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2109.69605</v>
+        <v>2335.00722</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:17</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>148.88172</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>149.14897</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>148.18685</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>79.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -626,14 +661,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -643,17 +678,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
@@ -663,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
@@ -673,38 +708,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.28</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07:35</t>
+          <t>2026-03-16 16:21:47</t>
         </is>
       </c>
     </row>
@@ -723,52 +758,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -777,12 +812,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-16 16:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -791,22 +826,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2638.81797</v>
+        <v>4041.71933</v>
       </c>
       <c r="E2" t="n">
-        <v>2638.81536</v>
+        <v>4041.71718</v>
       </c>
       <c r="F2" t="n">
-        <v>2638.82472</v>
+        <v>4041.72653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -817,36 +852,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:56</t>
+          <t>2026-03-16 16:11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5863</v>
+        <v>4053.58139</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58862</v>
+        <v>4053.57687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58136</v>
+        <v>4053.58917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -857,12 +892,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:43</t>
+          <t>2026-03-16 15:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,22 +906,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10395</v>
+        <v>2089.53047</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10659</v>
+        <v>2089.5336</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09987</v>
+        <v>2089.52097</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>3.03</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -897,36 +932,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:54</t>
+          <t>2026-03-16 16:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3602.6381</v>
+        <v>2109.02949</v>
       </c>
       <c r="E5" t="n">
-        <v>3602.64162</v>
+        <v>2109.02707</v>
       </c>
       <c r="F5" t="n">
-        <v>3602.63223</v>
+        <v>2109.03469</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -937,92 +972,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-16 16:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4064.91481</v>
+        <v>2350.37259</v>
       </c>
       <c r="E6" t="n">
-        <v>4064.91121</v>
+        <v>2350.37528</v>
       </c>
       <c r="F6" t="n">
-        <v>4064.91896</v>
+        <v>2350.36407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
+        <v>3.17</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-16 16:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2109.70362</v>
+        <v>1.11046</v>
       </c>
       <c r="E7" t="n">
-        <v>2109.7061</v>
+        <v>1.10565</v>
       </c>
       <c r="F7" t="n">
-        <v>2109.69605</v>
+        <v>1.11862</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>1.69</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2026-03-16 16:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1031,22 +1066,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3637.04486</v>
+        <v>2425.15733</v>
       </c>
       <c r="E8" t="n">
-        <v>3637.0413</v>
+        <v>2425.15344</v>
       </c>
       <c r="F8" t="n">
-        <v>3637.05461</v>
+        <v>2425.16458</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="n">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1057,12 +1092,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:33</t>
+          <t>2026-03-16 16:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,22 +1106,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2330.19431</v>
+        <v>2659.71606</v>
       </c>
       <c r="E9" t="n">
-        <v>2330.19843</v>
+        <v>2659.71882</v>
       </c>
       <c r="F9" t="n">
-        <v>2330.18961</v>
+        <v>2659.71166</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1097,116 +1132,116 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-16 16:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2654.13881</v>
+        <v>0.58709</v>
       </c>
       <c r="E10" t="n">
-        <v>2654.13442</v>
+        <v>0.58994</v>
       </c>
       <c r="F10" t="n">
-        <v>2654.14534</v>
+        <v>0.58014</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:52</t>
+          <t>2026-03-16 16:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2414.83832</v>
+        <v>2328.32011</v>
       </c>
       <c r="E11" t="n">
-        <v>2414.84059</v>
+        <v>2328.31705</v>
       </c>
       <c r="F11" t="n">
-        <v>2414.82938</v>
+        <v>2328.32853</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>2.75</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:59</t>
+          <t>2026-03-16 16:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58938</v>
+        <v>2092.42194</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59428</v>
+        <v>2092.41962</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58413</v>
+        <v>2092.42656</v>
       </c>
       <c r="G12" t="n">
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.07</v>
+        <v>1.99</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1217,92 +1252,92 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 21:25</t>
+          <t>2026-03-16 16:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10743</v>
+        <v>2335.0146</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10362</v>
+        <v>2335.01789</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1122</v>
+        <v>2335.00722</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 21:30</t>
+          <t>2026-03-16 16:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412.942</v>
+        <v>148.88172</v>
       </c>
       <c r="E14" t="n">
-        <v>2412.93763</v>
+        <v>149.14897</v>
       </c>
       <c r="F14" t="n">
-        <v>2412.94933</v>
+        <v>148.18685</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 21:35</t>
+          <t>2026-03-16 16:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1311,22 +1346,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3615</v>
+        <v>1.10006</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36633</v>
+        <v>1.10334</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35425</v>
+        <v>1.09159</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1337,36 +1372,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07</t>
+          <t>2026-03-16 16:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88156</v>
+        <v>2408.7724</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87934</v>
+        <v>2408.77702</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88597</v>
+        <v>2408.76777</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,13 +84,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -523,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:42</t>
+          <t>2026-03-16 17:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -537,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.58709</v>
+        <v>2659.40108</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.58994</v>
+        <v>2659.40345</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.58014</v>
+        <v>2659.39265</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -565,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:49</t>
+          <t>2026-03-16 17:16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2335.0146</v>
+        <v>0.66182</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2335.01789</v>
+        <v>0.65742</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2335.00722</v>
+        <v>0.66881</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -607,7 +614,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:17</t>
+          <t>2026-03-16 16:52</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -615,32 +622,284 @@
           <t>USDJPY</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>149.05982</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>148.7841</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>149.89634</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>89.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:32</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>149.34215</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>149.05025</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>149.7848</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:44</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>XAUGBP</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2109.53942</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2109.53685</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2109.54572</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>81.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:59</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>XAUGBP</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2089.86587</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2089.86294</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2089.87109</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:25</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>XAUAUD</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4043.55689</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4043.55367</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4043.5642</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95.0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>XAUCAD</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3628.77291</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3628.77021</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>3628.78245</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>86.0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:50</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>148.88172</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>149.14897</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>148.18685</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79.0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n">
+        <v>2335.67742</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2335.68068</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>2335.67042</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86.0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -661,14 +920,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -678,17 +937,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
@@ -698,7 +957,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
@@ -708,38 +967,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-16 16:21:47</t>
+          <t>2026-03-16 17:18:47</t>
         </is>
       </c>
     </row>
@@ -758,52 +1017,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -812,172 +1071,172 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27</t>
+          <t>2026-03-16 17:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4041.71933</v>
+        <v>2659.40108</v>
       </c>
       <c r="E2" t="n">
-        <v>4041.71718</v>
+        <v>2659.40345</v>
       </c>
       <c r="F2" t="n">
-        <v>4041.72653</v>
+        <v>2659.39265</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16 16:11</t>
+          <t>2026-03-16 17:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4053.58139</v>
+        <v>1.26885</v>
       </c>
       <c r="E3" t="n">
-        <v>4053.57687</v>
+        <v>1.2718</v>
       </c>
       <c r="F3" t="n">
-        <v>4053.58917</v>
+        <v>1.26319</v>
       </c>
       <c r="G3" t="n">
         <v>0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16 15:52</t>
+          <t>2026-03-16 17:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2089.53047</v>
+        <v>0.66182</v>
       </c>
       <c r="E4" t="n">
-        <v>2089.5336</v>
+        <v>0.65742</v>
       </c>
       <c r="F4" t="n">
-        <v>2089.52097</v>
+        <v>0.66881</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="I4" t="n">
-        <v>3.03</v>
+        <v>1.59</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16 16:45</t>
+          <t>2026-03-16 16:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2109.02949</v>
+        <v>1.1052</v>
       </c>
       <c r="E5" t="n">
-        <v>2109.02707</v>
+        <v>1.10855</v>
       </c>
       <c r="F5" t="n">
-        <v>2109.03469</v>
+        <v>1.09981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16 16:13</t>
+          <t>2026-03-16 16:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +1245,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2350.37259</v>
+        <v>1.26592</v>
       </c>
       <c r="E6" t="n">
-        <v>2350.37528</v>
+        <v>1.2699</v>
       </c>
       <c r="F6" t="n">
-        <v>2350.36407</v>
+        <v>1.26181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>3.17</v>
+        <v>1.03</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1012,36 +1271,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:16</t>
+          <t>2026-03-16 17:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.11046</v>
+        <v>1.26854</v>
       </c>
       <c r="E7" t="n">
-        <v>1.10565</v>
+        <v>1.27302</v>
       </c>
       <c r="F7" t="n">
-        <v>1.11862</v>
+        <v>1.26231</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1052,12 +1311,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16 16:31</t>
+          <t>2026-03-16 16:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1066,78 +1325,78 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2425.15733</v>
+        <v>149.05982</v>
       </c>
       <c r="E8" t="n">
-        <v>2425.15344</v>
+        <v>148.7841</v>
       </c>
       <c r="F8" t="n">
-        <v>2425.16458</v>
+        <v>149.89634</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="n">
         <v>0.89</v>
       </c>
       <c r="I8" t="n">
-        <v>1.86</v>
+        <v>3.03</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16 16:19</t>
+          <t>2026-03-16 17:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2659.71606</v>
+        <v>149.34215</v>
       </c>
       <c r="E9" t="n">
-        <v>2659.71882</v>
+        <v>149.05025</v>
       </c>
       <c r="F9" t="n">
-        <v>2659.71166</v>
+        <v>149.7848</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16 16:42</t>
+          <t>2026-03-16 16:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1146,38 +1405,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.58709</v>
+        <v>2343.325</v>
       </c>
       <c r="E10" t="n">
-        <v>0.58994</v>
+        <v>2343.32995</v>
       </c>
       <c r="F10" t="n">
-        <v>0.58014</v>
+        <v>2343.31765</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="I10" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16 16:19</t>
+          <t>2026-03-16 17:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1186,62 +1445,62 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2328.32011</v>
+        <v>2109.53942</v>
       </c>
       <c r="E11" t="n">
-        <v>2328.31705</v>
+        <v>2109.53685</v>
       </c>
       <c r="F11" t="n">
-        <v>2328.32853</v>
+        <v>2109.54572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16 16:29</t>
+          <t>2026-03-16 17:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2092.42194</v>
+        <v>2427.41561</v>
       </c>
       <c r="E12" t="n">
-        <v>2092.41962</v>
+        <v>2427.41913</v>
       </c>
       <c r="F12" t="n">
-        <v>2092.42656</v>
+        <v>2427.40775</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1252,36 +1511,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:49</t>
+          <t>2026-03-16 16:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2335.0146</v>
+        <v>2089.86587</v>
       </c>
       <c r="E13" t="n">
-        <v>2335.01789</v>
+        <v>2089.86294</v>
       </c>
       <c r="F13" t="n">
-        <v>2335.00722</v>
+        <v>2089.87109</v>
       </c>
       <c r="G13" t="n">
         <v>0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1292,36 +1551,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16 16:17</t>
+          <t>2026-03-16 17:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>148.88172</v>
+        <v>4043.55689</v>
       </c>
       <c r="E14" t="n">
-        <v>149.14897</v>
+        <v>4043.55367</v>
       </c>
       <c r="F14" t="n">
-        <v>148.18685</v>
+        <v>4043.5642</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1332,40 +1591,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16 16:15</t>
+          <t>2026-03-16 17:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.10006</v>
+        <v>3628.77291</v>
       </c>
       <c r="E15" t="n">
-        <v>1.10334</v>
+        <v>3628.77021</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09159</v>
+        <v>3628.78245</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>3.52</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1636,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1386,26 +1645,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2408.7724</v>
+        <v>2335.67742</v>
       </c>
       <c r="E16" t="n">
-        <v>2408.77702</v>
+        <v>2335.68068</v>
       </c>
       <c r="F16" t="n">
-        <v>2408.76777</v>
+        <v>2335.67042</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H16" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:26</t>
+          <t>2026-03-16 17:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2659.40108</v>
+        <v>2408.85066</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2659.40345</v>
+        <v>2408.85555</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2659.39265</v>
+        <v>2408.84416</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.55</v>
+        <v>1.33</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:16</t>
+          <t>2026-03-16 17:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -586,24 +586,24 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.66182</v>
+        <v>0.65696</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.65742</v>
+        <v>0.65247</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.66881</v>
+        <v>0.6654</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:52</t>
+          <t>2026-03-16 18:13</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>XAUGBP</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>149.05982</v>
+        <v>2092.03155</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.7841</v>
+        <v>2092.03564</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>149.89634</v>
+        <v>2092.02659</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3.03</v>
+        <v>1.22</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,12 +656,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:32</t>
+          <t>2026-03-16 17:48</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -670,24 +670,24 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>149.34215</v>
+        <v>0.66069</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>149.05025</v>
+        <v>0.65621</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>149.7848</v>
+        <v>0.66873</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -698,12 +698,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:44</t>
+          <t>2026-03-16 18:06</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -712,24 +712,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2109.53942</v>
+        <v>2639.42173</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2109.53685</v>
+        <v>2639.41742</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2109.54572</v>
+        <v>2639.42613</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.45</v>
+        <v>1.02</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:59</t>
+          <t>2026-03-16 17:59</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2089.86587</v>
+        <v>1.10802</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2089.86294</v>
+        <v>1.11172</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2089.87109</v>
+        <v>1.10154</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -782,124 +782,40 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:25</t>
+          <t>2026-03-16 17:28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4043.55689</v>
+        <v>149.23786</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4043.55367</v>
+        <v>149.55133</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4043.5642</v>
+        <v>148.73212</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2.27</v>
+        <v>1.61</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-16 17:01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>XAUCAD</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>3628.77291</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3628.77021</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>3628.78245</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>86.0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-16 16:50</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>XAUCHF</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>2335.67742</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2335.68068</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>2335.67042</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86.0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -943,7 +859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -953,7 +869,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -963,7 +879,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -974,7 +890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -986,7 +902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -998,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-16 17:18:47</t>
+          <t>2026-03-16 17:43:46</t>
         </is>
       </c>
     </row>
@@ -1071,7 +987,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:26</t>
+          <t>2026-03-16 18:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1081,42 +997,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2659.40108</v>
+        <v>2649.49451</v>
       </c>
       <c r="E2" t="n">
-        <v>2659.40345</v>
+        <v>2649.49222</v>
       </c>
       <c r="F2" t="n">
-        <v>2659.39265</v>
+        <v>2649.50335</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16 17:19</t>
+          <t>2026-03-16 17:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1125,38 +1041,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.26885</v>
+        <v>2408.85066</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2718</v>
+        <v>2408.85555</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26319</v>
+        <v>2408.84416</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16 17:16</t>
+          <t>2026-03-16 18:11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1165,38 +1081,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.66182</v>
+        <v>3603.76216</v>
       </c>
       <c r="E4" t="n">
-        <v>0.65742</v>
+        <v>3603.75945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66881</v>
+        <v>3603.76985</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16 16:50</t>
+          <t>2026-03-16 18:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1205,22 +1121,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.1052</v>
+        <v>1.3612</v>
       </c>
       <c r="E5" t="n">
-        <v>1.10855</v>
+        <v>1.36345</v>
       </c>
       <c r="F5" t="n">
-        <v>1.09981</v>
+        <v>1.35654</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1231,52 +1147,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16 16:53</t>
+          <t>2026-03-16 17:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.26592</v>
+        <v>0.65696</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2699</v>
+        <v>0.65247</v>
       </c>
       <c r="F6" t="n">
-        <v>1.26181</v>
+        <v>0.6654</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16 17:20</t>
+          <t>2026-03-16 18:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1285,38 +1201,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.26854</v>
+        <v>2092.03155</v>
       </c>
       <c r="E7" t="n">
-        <v>1.27302</v>
+        <v>2092.03564</v>
       </c>
       <c r="F7" t="n">
-        <v>1.26231</v>
+        <v>2092.02659</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16 16:52</t>
+          <t>2026-03-16 17:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,38 +1241,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>149.05982</v>
+        <v>2351.12802</v>
       </c>
       <c r="E8" t="n">
-        <v>148.7841</v>
+        <v>2351.12458</v>
       </c>
       <c r="F8" t="n">
-        <v>149.89634</v>
+        <v>2351.1335</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>3.03</v>
+        <v>1.59</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16 17:32</t>
+          <t>2026-03-16 18:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1365,78 +1281,78 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149.34215</v>
+        <v>2100.47595</v>
       </c>
       <c r="E9" t="n">
-        <v>149.05025</v>
+        <v>2100.47284</v>
       </c>
       <c r="F9" t="n">
-        <v>149.7848</v>
+        <v>2100.48329</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H9" t="n">
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16 16:59</t>
+          <t>2026-03-16 17:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2343.325</v>
+        <v>0.66069</v>
       </c>
       <c r="E10" t="n">
-        <v>2343.32995</v>
+        <v>0.65621</v>
       </c>
       <c r="F10" t="n">
-        <v>2343.31765</v>
+        <v>0.66873</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16 17:44</t>
+          <t>2026-03-16 17:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1445,78 +1361,78 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2109.53942</v>
+        <v>150.0771</v>
       </c>
       <c r="E11" t="n">
-        <v>2109.53685</v>
+        <v>149.81353</v>
       </c>
       <c r="F11" t="n">
-        <v>2109.54572</v>
+        <v>150.72007</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16 17:08</t>
+          <t>2026-03-16 18:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2427.41561</v>
+        <v>2639.42173</v>
       </c>
       <c r="E12" t="n">
-        <v>2427.41913</v>
+        <v>2639.41742</v>
       </c>
       <c r="F12" t="n">
-        <v>2427.40775</v>
+        <v>2639.42613</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H12" t="n">
         <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:59</t>
+          <t>2026-03-16 17:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1525,62 +1441,62 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2089.86587</v>
+        <v>2343.81053</v>
       </c>
       <c r="E13" t="n">
-        <v>2089.86294</v>
+        <v>2343.80555</v>
       </c>
       <c r="F13" t="n">
-        <v>2089.87109</v>
+        <v>2343.81633</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I13" t="n">
-        <v>1.77</v>
+        <v>1.17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16 17:25</t>
+          <t>2026-03-16 17:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4043.55689</v>
+        <v>1.10802</v>
       </c>
       <c r="E14" t="n">
-        <v>4043.55367</v>
+        <v>1.11172</v>
       </c>
       <c r="F14" t="n">
-        <v>4043.5642</v>
+        <v>1.10154</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1591,12 +1507,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16 17:01</t>
+          <t>2026-03-16 17:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1605,38 +1521,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3628.77291</v>
+        <v>2105.25727</v>
       </c>
       <c r="E15" t="n">
-        <v>3628.77021</v>
+        <v>2105.2536</v>
       </c>
       <c r="F15" t="n">
-        <v>3628.78245</v>
+        <v>2105.26193</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>3.52</v>
+        <v>1.27</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16 16:50</t>
+          <t>2026-03-16 17:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1645,22 +1561,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2335.67742</v>
+        <v>149.23786</v>
       </c>
       <c r="E16" t="n">
-        <v>2335.68068</v>
+        <v>149.55133</v>
       </c>
       <c r="F16" t="n">
-        <v>2335.67042</v>
+        <v>148.73212</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H16" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,38 +530,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:48</t>
+          <t>2026-03-16 19:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2408.85066</v>
+        <v>0.58792</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2408.85555</v>
+        <v>0.5857</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2408.84416</v>
+        <v>0.59506</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.33</v>
+        <v>3.23</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,38 +572,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:51</t>
+          <t>2026-03-16 19:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.65696</v>
+        <v>4042.85873</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.65247</v>
+        <v>4042.86084</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6654</v>
+        <v>4042.85163</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.88</v>
+        <v>3.37</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 18:13</t>
+          <t>2026-03-16 19:33</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+          <t>XAUEUR</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2092.03155</v>
+        <v>2419.51792</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2092.03564</v>
+        <v>2419.52014</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2092.02659</v>
+        <v>2419.51071</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.22</v>
+        <v>3.25</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:48</t>
+          <t>2026-03-16 19:16</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.66069</v>
+        <v>150.07601</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.65621</v>
+        <v>149.79958</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.66873</v>
+        <v>150.68093</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -698,38 +698,38 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 18:06</t>
+          <t>2026-03-16 19:36</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2639.42173</v>
+        <v>150.07973</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2639.41742</v>
+        <v>149.6294</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2639.42613</v>
+        <v>150.484</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:59</t>
+          <t>2026-03-16 19:41</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EURUSD</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+          <t>XAUAUD</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.10802</v>
+        <v>4053.86571</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.11172</v>
+        <v>4053.86792</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.10154</v>
+        <v>4053.85572</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -782,38 +782,38 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16 17:28</t>
+          <t>2026-03-16 19:45</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>149.23786</v>
+        <v>0.88124</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>149.55133</v>
+        <v>0.87678</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>148.73212</v>
+        <v>0.88739</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -890,7 +890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>88.5%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-16 17:43:46</t>
+          <t>2026-03-16 19:24:15</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16 18:12</t>
+          <t>2026-03-16 19:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1001,73 +1001,73 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2649.49451</v>
+        <v>0.58792</v>
       </c>
       <c r="E2" t="n">
-        <v>2649.49222</v>
+        <v>0.5857</v>
       </c>
       <c r="F2" t="n">
-        <v>2649.50335</v>
+        <v>0.59506</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.86</v>
+        <v>3.23</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16 17:48</t>
+          <t>2026-03-16 19:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2408.85066</v>
+        <v>3635.30066</v>
       </c>
       <c r="E3" t="n">
-        <v>2408.85555</v>
+        <v>3635.29649</v>
       </c>
       <c r="F3" t="n">
-        <v>2408.84416</v>
+        <v>3635.30817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16 18:11</t>
+          <t>2026-03-16 19:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1077,26 +1077,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3603.76216</v>
+        <v>3603.17182</v>
       </c>
       <c r="E4" t="n">
-        <v>3603.75945</v>
+        <v>3603.17615</v>
       </c>
       <c r="F4" t="n">
-        <v>3603.76985</v>
+        <v>3603.16615</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>1.31</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1107,36 +1107,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16 18:13</t>
+          <t>2026-03-16 19:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3612</v>
+        <v>0.65657</v>
       </c>
       <c r="E5" t="n">
-        <v>1.36345</v>
+        <v>0.65249</v>
       </c>
       <c r="F5" t="n">
-        <v>1.35654</v>
+        <v>0.66592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16 17:51</t>
+          <t>2026-03-16 19:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1161,38 +1161,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.65696</v>
+        <v>1.10129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.65247</v>
+        <v>1.09697</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6654</v>
+        <v>1.11077</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16 18:13</t>
+          <t>2026-03-16 19:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,22 +1201,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2092.03155</v>
+        <v>4042.85873</v>
       </c>
       <c r="E7" t="n">
-        <v>2092.03564</v>
+        <v>4042.86084</v>
       </c>
       <c r="F7" t="n">
-        <v>2092.02659</v>
+        <v>4042.85163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>1.22</v>
+        <v>3.37</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1227,92 +1227,92 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16 17:34</t>
+          <t>2026-03-16 19:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2351.12802</v>
+        <v>0.87744</v>
       </c>
       <c r="E8" t="n">
-        <v>2351.12458</v>
+        <v>0.88113</v>
       </c>
       <c r="F8" t="n">
-        <v>2351.1335</v>
+        <v>0.86782</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>1.59</v>
+        <v>2.61</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16 18:08</t>
+          <t>2026-03-16 19:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2100.47595</v>
+        <v>2419.51792</v>
       </c>
       <c r="E9" t="n">
-        <v>2100.47284</v>
+        <v>2419.52014</v>
       </c>
       <c r="F9" t="n">
-        <v>2100.48329</v>
+        <v>2419.51071</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16 17:48</t>
+          <t>2026-03-16 19:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1321,22 +1321,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.66069</v>
+        <v>150.07601</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65621</v>
+        <v>149.79958</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66873</v>
+        <v>150.68093</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1347,36 +1347,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16 17:25</t>
+          <t>2026-03-16 19:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150.0771</v>
+        <v>0.58808</v>
       </c>
       <c r="E11" t="n">
-        <v>149.81353</v>
+        <v>0.59117</v>
       </c>
       <c r="F11" t="n">
-        <v>150.72007</v>
+        <v>0.5828</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H11" t="n">
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1387,12 +1387,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16 18:06</t>
+          <t>2026-03-16 19:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2639.42173</v>
+        <v>150.07973</v>
       </c>
       <c r="E12" t="n">
-        <v>2639.41742</v>
+        <v>149.6294</v>
       </c>
       <c r="F12" t="n">
-        <v>2639.42613</v>
+        <v>150.484</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1427,52 +1427,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16 17:29</t>
+          <t>2026-03-16 19:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2343.81053</v>
+        <v>4053.86571</v>
       </c>
       <c r="E13" t="n">
-        <v>2343.80555</v>
+        <v>4053.86792</v>
       </c>
       <c r="F13" t="n">
-        <v>2343.81633</v>
+        <v>4053.85572</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>1.17</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16 17:59</t>
+          <t>2026-03-16 19:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1481,38 +1481,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.10802</v>
+        <v>0.59114</v>
       </c>
       <c r="E14" t="n">
-        <v>1.11172</v>
+        <v>0.59495</v>
       </c>
       <c r="F14" t="n">
-        <v>1.10154</v>
+        <v>0.58599</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16 17:20</t>
+          <t>2026-03-16 19:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1521,66 +1521,66 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2105.25727</v>
+        <v>0.88124</v>
       </c>
       <c r="E15" t="n">
-        <v>2105.2536</v>
+        <v>0.87678</v>
       </c>
       <c r="F15" t="n">
-        <v>2105.26193</v>
+        <v>0.88739</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16 17:28</t>
+          <t>2026-03-16 19:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>149.23786</v>
+        <v>1.27486</v>
       </c>
       <c r="E16" t="n">
-        <v>149.55133</v>
+        <v>1.27113</v>
       </c>
       <c r="F16" t="n">
-        <v>148.73212</v>
+        <v>1.28437</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-19 14:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -540,28 +540,28 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4064.91481</v>
+        <v>4059.83292</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4064.91121</v>
+        <v>4059.83574</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4064.91896</v>
+        <v>4059.82522</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.15</v>
+        <v>2.73</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,40 +572,166 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-19 14:25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2109.70362</v>
+        <v>2655.13793</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2109.7061</v>
+        <v>2655.14246</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2109.69605</v>
+        <v>2655.13291</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>84.0%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:53</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.58817</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.59638</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:57</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2339.35362</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2339.34916</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2339.36054</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>84.0%</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:17</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>XAUCHF</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2331.18375</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2331.1874</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2331.17646</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -649,7 +775,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +785,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +795,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -680,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>86.9%</t>
         </is>
       </c>
     </row>
@@ -692,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -704,7 +830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07:35</t>
+          <t>2026-03-19 14:46:35</t>
         </is>
       </c>
     </row>
@@ -777,92 +903,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-19 14:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2638.81797</v>
+        <v>4059.83292</v>
       </c>
       <c r="E2" t="n">
-        <v>2638.81536</v>
+        <v>4059.83574</v>
       </c>
       <c r="F2" t="n">
-        <v>2638.82472</v>
+        <v>4059.82522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:56</t>
+          <t>2026-03-19 15:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5863</v>
+        <v>3635.4112</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58862</v>
+        <v>3635.40852</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58136</v>
+        <v>3635.41524</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:43</t>
+          <t>2026-03-19 14:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,38 +997,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10395</v>
+        <v>2655.13793</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10659</v>
+        <v>2655.14246</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09987</v>
+        <v>2655.13291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:54</t>
+          <t>2026-03-19 15:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -911,38 +1037,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3602.6381</v>
+        <v>0.65805</v>
       </c>
       <c r="E5" t="n">
-        <v>3602.64162</v>
+        <v>0.66181</v>
       </c>
       <c r="F5" t="n">
-        <v>3602.63223</v>
+        <v>0.65166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-19 14:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,78 +1077,78 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4064.91481</v>
+        <v>0.87907</v>
       </c>
       <c r="E6" t="n">
-        <v>4064.91121</v>
+        <v>0.8766699999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4064.91896</v>
+        <v>0.88442</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
+        <v>2.23</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-19 15:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2109.70362</v>
+        <v>0.59082</v>
       </c>
       <c r="E7" t="n">
-        <v>2109.7061</v>
+        <v>0.5880300000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2109.69605</v>
+        <v>0.59519</v>
       </c>
       <c r="G7" t="n">
         <v>0.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>1.57</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2026-03-19 14:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1031,22 +1157,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3637.04486</v>
+        <v>2655.56426</v>
       </c>
       <c r="E8" t="n">
-        <v>3637.0413</v>
+        <v>2655.56213</v>
       </c>
       <c r="F8" t="n">
-        <v>3637.05461</v>
+        <v>2655.57381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="I8" t="n">
-        <v>2.75</v>
+        <v>4.49</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1057,76 +1183,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:33</t>
+          <t>2026-03-19 14:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2330.19431</v>
+        <v>0.58817</v>
       </c>
       <c r="E9" t="n">
-        <v>2330.19843</v>
+        <v>0.5851</v>
       </c>
       <c r="F9" t="n">
-        <v>2330.18961</v>
+        <v>0.59638</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.14</v>
+        <v>2.67</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-19 14:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2654.13881</v>
+        <v>3630.13728</v>
       </c>
       <c r="E10" t="n">
-        <v>2654.13442</v>
+        <v>3630.14103</v>
       </c>
       <c r="F10" t="n">
-        <v>2654.14534</v>
+        <v>3630.13069</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1137,12 +1263,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:52</t>
+          <t>2026-03-19 15:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1151,22 +1277,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2414.83832</v>
+        <v>1.102</v>
       </c>
       <c r="E11" t="n">
-        <v>2414.84059</v>
+        <v>1.10681</v>
       </c>
       <c r="F11" t="n">
-        <v>2414.82938</v>
+        <v>1.09574</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1177,36 +1303,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:59</t>
+          <t>2026-03-19 15:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58938</v>
+        <v>0.87979</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59428</v>
+        <v>0.8753300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58413</v>
+        <v>0.88647</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="I12" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1217,12 +1343,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 21:25</t>
+          <t>2026-03-19 14:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1231,22 +1357,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10743</v>
+        <v>1.35896</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10362</v>
+        <v>1.35549</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1122</v>
+        <v>1.36335</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1257,12 +1383,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 21:30</t>
+          <t>2026-03-19 14:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1271,38 +1397,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412.942</v>
+        <v>2339.35362</v>
       </c>
       <c r="E14" t="n">
-        <v>2412.93763</v>
+        <v>2339.34916</v>
       </c>
       <c r="F14" t="n">
-        <v>2412.94933</v>
+        <v>2339.36054</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 21:35</t>
+          <t>2026-03-19 14:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>XAUCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1311,38 +1437,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3615</v>
+        <v>2331.18375</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36633</v>
+        <v>2331.1874</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35425</v>
+        <v>2331.17646</v>
       </c>
       <c r="G15" t="n">
         <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07</t>
+          <t>2026-03-19 14:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>XAUCAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1351,26 +1477,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88156</v>
+        <v>3632.32541</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87934</v>
+        <v>3632.32212</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88597</v>
+        <v>3632.33536</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>3.02</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,14 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -460,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-24 05:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +537,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4064.91481</v>
+        <v>1.36584</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4064.91121</v>
+        <v>1.36216</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4064.91896</v>
+        <v>1.37431</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,40 +565,166 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-24 06:06</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.36396</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1.36041</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1.37095</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>79.0%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 06:21</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>XAUGBP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2109.70362</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2109.7061</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2109.69605</v>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2109.28047</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2109.27773</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2109.28521</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 06:00</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.88171</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.87837</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.89093</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 06:19</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.65549</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.65328</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.66223</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>84.0%</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>3.04</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -626,14 +745,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>GenX FX Trading Dashboard</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Signals</t>
         </is>
@@ -643,17 +762,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Active Signals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BUY Signals</t>
         </is>
@@ -663,7 +782,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>SELL Signals</t>
         </is>
@@ -673,38 +792,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Average Confidence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>85.8%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Average Risk/Reward</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.58</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07:35</t>
+          <t>2026-03-24 05:54:20</t>
         </is>
       </c>
     </row>
@@ -723,52 +842,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -777,12 +896,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-24 05:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -791,38 +910,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2638.81797</v>
+        <v>2102.82189</v>
       </c>
       <c r="E2" t="n">
-        <v>2638.81536</v>
+        <v>2102.81972</v>
       </c>
       <c r="F2" t="n">
-        <v>2638.82472</v>
+        <v>2102.82991</v>
       </c>
       <c r="G2" t="n">
         <v>0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.59</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:56</t>
+          <t>2026-03-24 06:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -831,38 +950,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5863</v>
+        <v>1.27503</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58862</v>
+        <v>1.27756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58136</v>
+        <v>1.26644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>3.39</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:43</t>
+          <t>2026-03-24 06:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,22 +990,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10395</v>
+        <v>4048.64362</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10659</v>
+        <v>4048.6462</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09987</v>
+        <v>4048.63817</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -897,12 +1016,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:54</t>
+          <t>2026-03-24 05:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -911,22 +1030,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3602.6381</v>
+        <v>0.65987</v>
       </c>
       <c r="E5" t="n">
-        <v>3602.64162</v>
+        <v>0.66391</v>
       </c>
       <c r="F5" t="n">
-        <v>3602.63223</v>
+        <v>0.65215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -937,12 +1056,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-24 05:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,38 +1070,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4064.91481</v>
+        <v>1.36447</v>
       </c>
       <c r="E6" t="n">
-        <v>4064.91121</v>
+        <v>1.36106</v>
       </c>
       <c r="F6" t="n">
-        <v>4064.91896</v>
+        <v>1.37334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-24 05:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -991,142 +1110,142 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2109.70362</v>
+        <v>4042.7444</v>
       </c>
       <c r="E7" t="n">
-        <v>2109.7061</v>
+        <v>4042.74674</v>
       </c>
       <c r="F7" t="n">
-        <v>2109.69605</v>
+        <v>4042.73504</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>3.99</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2026-03-24 06:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3637.04486</v>
+        <v>1.27324</v>
       </c>
       <c r="E8" t="n">
-        <v>3637.0413</v>
+        <v>1.27541</v>
       </c>
       <c r="F8" t="n">
-        <v>3637.05461</v>
+        <v>1.26645</v>
       </c>
       <c r="G8" t="n">
         <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:33</t>
+          <t>2026-03-24 05:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2330.19431</v>
+        <v>1.36584</v>
       </c>
       <c r="E9" t="n">
-        <v>2330.19843</v>
+        <v>1.36216</v>
       </c>
       <c r="F9" t="n">
-        <v>2330.18961</v>
+        <v>1.37431</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-24 05:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2654.13881</v>
+        <v>2097.79258</v>
       </c>
       <c r="E10" t="n">
-        <v>2654.13442</v>
+        <v>2097.79559</v>
       </c>
       <c r="F10" t="n">
-        <v>2654.14534</v>
+        <v>2097.78475</v>
       </c>
       <c r="G10" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>2.61</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1137,12 +1256,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:52</t>
+          <t>2026-03-24 06:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1151,22 +1270,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2414.83832</v>
+        <v>1.27104</v>
       </c>
       <c r="E11" t="n">
-        <v>2414.84059</v>
+        <v>1.27518</v>
       </c>
       <c r="F11" t="n">
-        <v>2414.82938</v>
+        <v>1.26477</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>1.51</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1177,92 +1296,92 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:59</t>
+          <t>2026-03-24 06:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58938</v>
+        <v>1.36396</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59428</v>
+        <v>1.36041</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58413</v>
+        <v>1.37095</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="I12" t="n">
-        <v>1.07</v>
+        <v>1.97</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 21:25</t>
+          <t>2026-03-24 05:54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10743</v>
+        <v>0.65484</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10362</v>
+        <v>0.65972</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1122</v>
+        <v>0.64513</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 21:30</t>
+          <t>2026-03-24 06:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUGBP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1271,78 +1390,78 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412.942</v>
+        <v>2109.28047</v>
       </c>
       <c r="E14" t="n">
-        <v>2412.93763</v>
+        <v>2109.27773</v>
       </c>
       <c r="F14" t="n">
-        <v>2412.94933</v>
+        <v>2109.28521</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 21:35</t>
+          <t>2026-03-24 06:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3615</v>
+        <v>0.88171</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36633</v>
+        <v>0.87837</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35425</v>
+        <v>0.89093</v>
       </c>
       <c r="G15" t="n">
         <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.77</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07</t>
+          <t>2026-03-24 06:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1351,26 +1470,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88156</v>
+        <v>0.65549</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87934</v>
+        <v>0.65328</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88597</v>
+        <v>0.66223</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>3.04</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/signal_output/genx_signals.xlsx
+++ b/signal_output/genx_signals.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-24 08:25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4064.91481</v>
+        <v>0.88222</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4064.91121</v>
+        <v>0.8801099999999999</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4064.91896</v>
+        <v>0.89131</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.15</v>
+        <v>4.31</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -572,12 +572,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-24 08:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -586,26 +586,152 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2109.70362</v>
+        <v>0.58571</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2109.7061</v>
+        <v>0.59071</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2109.69605</v>
+        <v>0.57979</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.04</v>
+        <v>1.19</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 08:43</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>150.06398</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>150.36055</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>149.25888</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 08:34</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1.36267</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1.35987</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1.37227</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 08:56</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>XAUEUR</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2426.7202</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2426.72508</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2426.71033</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -649,7 +775,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +785,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +795,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -680,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
     </row>
@@ -692,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -704,7 +830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07:35</t>
+          <t>2026-03-24 08:44:13</t>
         </is>
       </c>
     </row>
@@ -777,87 +903,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-24 09:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2638.81797</v>
+        <v>1.26847</v>
       </c>
       <c r="E2" t="n">
-        <v>2638.81536</v>
+        <v>1.27086</v>
       </c>
       <c r="F2" t="n">
-        <v>2638.82472</v>
+        <v>1.26131</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-28 20:56</t>
+          <t>2026-03-24 08:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5863</v>
+        <v>0.88222</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58862</v>
+        <v>0.8801099999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58136</v>
+        <v>0.89131</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>4.31</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28 20:43</t>
+          <t>2026-03-24 08:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -867,26 +993,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.10395</v>
+        <v>1.10137</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10659</v>
+        <v>1.09789</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09987</v>
+        <v>1.10641</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H4" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -897,12 +1023,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-07-28 20:54</t>
+          <t>2026-03-24 08:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XAUCAD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -911,62 +1037,62 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3602.6381</v>
+        <v>0.58571</v>
       </c>
       <c r="E5" t="n">
-        <v>3602.64162</v>
+        <v>0.59071</v>
       </c>
       <c r="F5" t="n">
-        <v>3602.63223</v>
+        <v>0.57979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-07-28 21:28</t>
+          <t>2026-03-24 08:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUAUD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4064.91481</v>
+        <v>150.06398</v>
       </c>
       <c r="E6" t="n">
-        <v>4064.91121</v>
+        <v>150.36055</v>
       </c>
       <c r="F6" t="n">
-        <v>4064.91896</v>
+        <v>149.25888</v>
       </c>
       <c r="G6" t="n">
         <v>0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
+        <v>2.71</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -977,47 +1103,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-28 20:55</t>
+          <t>2026-03-24 08:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAUGBP</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2109.70362</v>
+        <v>2424.96166</v>
       </c>
       <c r="E7" t="n">
-        <v>2109.7061</v>
+        <v>2424.95679</v>
       </c>
       <c r="F7" t="n">
-        <v>2109.69605</v>
+        <v>2424.97108</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>1.93</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28 20:40</t>
+          <t>2026-03-24 08:38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1027,42 +1153,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3637.04486</v>
+        <v>3628.6079</v>
       </c>
       <c r="E8" t="n">
-        <v>3637.0413</v>
+        <v>3628.61028</v>
       </c>
       <c r="F8" t="n">
-        <v>3637.05461</v>
+        <v>3628.60271</v>
       </c>
       <c r="G8" t="n">
         <v>0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-28 21:33</t>
+          <t>2026-03-24 09:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XAUCHF</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,38 +1197,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2330.19431</v>
+        <v>0.58951</v>
       </c>
       <c r="E9" t="n">
-        <v>2330.19843</v>
+        <v>0.59372</v>
       </c>
       <c r="F9" t="n">
-        <v>2330.18961</v>
+        <v>0.5828100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-28 21:19</t>
+          <t>2026-03-24 08:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1111,38 +1237,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2654.13881</v>
+        <v>1.36267</v>
       </c>
       <c r="E10" t="n">
-        <v>2654.13442</v>
+        <v>1.35987</v>
       </c>
       <c r="F10" t="n">
-        <v>2654.14534</v>
+        <v>1.37227</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H10" t="n">
         <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>1.48</v>
+        <v>3.43</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-28 20:52</t>
+          <t>2026-03-24 08:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>XAUAUD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1151,118 +1277,118 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2414.83832</v>
+        <v>4069.32751</v>
       </c>
       <c r="E11" t="n">
-        <v>2414.84059</v>
+        <v>4069.33012</v>
       </c>
       <c r="F11" t="n">
-        <v>2414.82938</v>
+        <v>4069.32024</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>2.78</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-28 20:59</t>
+          <t>2026-03-24 08:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58938</v>
+        <v>1.26678</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59428</v>
+        <v>1.26341</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58413</v>
+        <v>1.27145</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H12" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="I12" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-28 21:25</t>
+          <t>2026-03-24 08:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XAUEUR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.10743</v>
+        <v>2426.7202</v>
       </c>
       <c r="E13" t="n">
-        <v>1.10362</v>
+        <v>2426.72508</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1122</v>
+        <v>2426.71033</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>2.03</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07-28 21:30</t>
+          <t>2026-03-24 08:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XAUEUR</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1271,38 +1397,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412.942</v>
+        <v>149.47704</v>
       </c>
       <c r="E14" t="n">
-        <v>2412.93763</v>
+        <v>149.25328</v>
       </c>
       <c r="F14" t="n">
-        <v>2412.94933</v>
+        <v>150.33535</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>3.84</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-07-28 21:35</t>
+          <t>2026-03-24 08:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1311,22 +1437,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3615</v>
+        <v>1.10708</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36633</v>
+        <v>1.111</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35425</v>
+        <v>1.09918</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1337,40 +1463,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-07-28 21:07</t>
+          <t>2026-03-24 09:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.88156</v>
+        <v>0.65883</v>
       </c>
       <c r="E16" t="n">
-        <v>0.87934</v>
+        <v>0.66238</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88597</v>
+        <v>0.65357</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Filled</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
